--- a/Tax知识库回答及问题反馈_少问题.xlsx
+++ b/Tax知识库回答及问题反馈_少问题.xlsx
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D\AI_Rating_1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2917BED3-09D0-4FE5-A1D9-D772403CD5A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{893D74FF-73ED-433C-8D2F-8505FA9D324A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$T$1</definedName>
-  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="98">
   <si>
     <t>#</t>
   </si>
@@ -685,91 +682,2004 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>现有AI回答</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">核心发现
-在现行企业所得税法下，居民企业取得所得可能适用7.5%税率的情形，主要发生在享受15%优惠税率的企业处于"减半征收"期间的场景。7.5% = 15% × 50%，即企业在享受15%优惠税率的基础上，其特定所得又适用"减半征收"优惠。但需注意，现行法规对15%税率与减半征收的叠加适用有严格限制，大多数情形下不允许15%税率减半征收（即不允许7.5%税率），减半征收应以25%法定税率为基础（即12.5%）。仅在极少数过渡期政策场景下，7.5%税率才可能适用。
-风险评估
-叠加享受禁止风险：国税函[2010]157号明确禁止居民企业享受15%税率的减半征税，即不允许7.5%税率。实务中若企业错误地将15%优惠税率与减半征收叠加，存在被税务机关追缴税款及加收滞纳金的风险。
-过渡期政策到期风险：7.5%税率仅在特定的历史过渡期场景下存在，相关过渡优惠政策已陆续到期，适用范围极为有限。
-政策理解偏差风险：部分地方税务机关在2008年新税法实施初期曾允许老高新技术企业按15%税率减半征收（实际7.5%），但该做法已被后续法规明确纠正。
-核心建议
-一般原则：居民企业取得实施条例第八十六条（农林牧渔业减半项目）、第八十七条（公共基础设施减半期）、第八十八条（环保节能节水减半期）、第九十条（技术转让超过500万元部分减半）规定的可减半征收所得，应依照25%的法定税率减半缴纳企业所得税（即12.5%），而非15%税率减半（7.5%）。
-过渡期例外：仅在2008年新税法实施初期，老高新技术企业（2007年3月16日前设立）处于原"三免三减半"减半期内的，可按15%税率减半征收（实际7.5%），但该过渡期政策已到期。
-实务操作：企业如同时享受15%优惠税率（如高新技术企业、西部大开发企业等）和减半征收优惠，应选择其一，不得叠加享受15%税率的减半征收。
+    <t>在企业重组中，重组一方中有自然人股东的，是否影响企业重组适用特殊性税务处理？自然人能否适用特殊性税务处理，从而递延缴纳个人所得税？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>回答和分析都正确。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2024年，企业新购入软件300万元，可以一次性在税前扣除吗？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）查询一次性折旧/摊销规定，根据财税〔2018〕54号及延续政策如财政部、税务总局公告[2023]37号，“企业在2018年1月1​日至2027年12月31日期间新购进的设备、器具，单位价值不超过500万元的，允许一次性计入当期成本费用在计算应纳税所得额时扣除”。但相关规定只针对机器、设备。
+2）判别软件的种类及会计处理，属于固定资产还是属于无形资产。若属于固定资产，可以适用上述政策。若属于无形资产，进一步搜索到财税〔2020〕31号、财税〔2022〕19号，在海南及横琴，对于新购入的无形资产也可适用一次性扣除。
+3）若无法适用一次性扣除，进一步提供软件摊销的税务处理，检索到财税〔2012〕27号，软件作为无形资产或固定资产可按最低2年摊销的规定；以及《企业所得税法》无形资产不低于10年直线摊销的规定。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">财政部 税务总局关于设备 器具扣除有关企业所得税政策的通知（财税〔2018〕54号）
+https://fgk.chinatax.gov.cn/zcfgk/c102416/c5202450/content.html
+财政部税务总局关于设备、器具扣除有关企业所得税政策的公告（财政部、税务总局公告[2023]37号）
+https://fgk.chinatax.gov.cn/zcfgk/c102416/c5212306/content.html
+财政部 税务总局关于海南自由贸易港企业所得税优惠政策的通知（财税〔2020〕31号）
+https://fgk.chinatax.gov.cn/zcfgk/c102416/c5202204/content.html
+财政部 税务总局关于横琴粤澳深度合作区企业所得税优惠政策的通知（财税〔2022〕19号）
+https://www.hengqin.gov.cn/lab/zccx/gjzc/content/post_3510124.html
+关于进一步鼓励软件产业和集成电路产业发展企业所得税政策的通知（财税〔2012〕27号）
+https://fgk.chinatax.gov.cn/zcfgk/c102416/c5204290/content.html
+企业所得税法
+https://fgk.chinatax.gov.cn/zcfgk/c100009/c5193018/content.html
+企业所得税法实施条例
+https://fgk.chinatax.gov.cn/zcfgk/c100010/c5194417/content.html
+</t>
+  </si>
+  <si>
+    <t>根据现行企业所得税政策，2024年企业新购入软件300万元，若该软件在特定情况下并入机器设备核算，或企业位于海南自贸港、横琴粤澳深度合作区，该软件可以一次性税前扣除。否则应按无形资产在10年或2年内摊销。具体分析及政策如下：
+1. 财税〔2018〕54号及延续政策（有效期至2027年12月31日）
+企业在2018年1月1日至2027年12月31日期间新购进的设备、器具（指除房屋、建筑物以外的固定资产），单位价值不超过500万元的，允许一次性计入当期成本费用在计算应纳税所得额时扣除。
+须根据新购入软件的种类及会计处理判断是否属于"设备、器具"
+- 软件在会计上作为固定资产核算（例如软件构成设备不可分割部分），可能可以随设备一并享受政策，以主管税务机关口径为准。
+- 软件作为无形资产核算（单独软件），则不满足财税〔2018〕54号及延续政策的一次性扣除条件。
+2.特殊区域的规定：
+海南自由贸易港：根据 财税〔2020〕31号，2020年1月1日至2024年12月31日，新购置无形资产单位价值≤500万元，可一次性扣除
+横琴粤澳深度合作区：根据财税〔2022〕19号，也有无形资产一次性扣除政策
+3.全国通用政策（非一次性扣除）
+除上述两个特殊情形外，2024年，企业购入300万元软件无法适用一次性税前扣除，一般软件折旧/摊销相关税收政策为：
+a.按《企业所得税法》，无形资产最低摊销年限为10年，直线法扣除
+b. 缩短摊销年限政策
+依据财税〔2012〕27号，企业外购的软件，符合固定资产或无形资产确认条件的，折旧或摊销年限可以选择缩短至最短2年（含）。</t>
+  </si>
+  <si>
+    <t>1）直接根据一次性扣除政策判断可以享受一次性扣除。
+2）直接判断软件不属于设备、器具，不符合一次性扣除条件，未对软件的性质和会计处理进行分类讨论，该判断可能对AI语义理解要求比较高，还要结合会计处理的规定
+3）未检索到特殊区域对于无形资产一次性摊销的特殊规定</t>
+  </si>
+  <si>
+    <t>核心结论
+2024年企业新购入软件300万元，能否一次性税前扣除，取决于该软件在会计上是作为"固定资产"还是"无形资产"核算：
+核算方式	能否一次性扣除	政策依据
+作为固定资产核算	可以一次性扣除（不超过500万元）	财政部、税务总局公告[2023]37号1
+作为无形资产核算	不能一次性扣除，需分期摊销	《企业所得税法实施条例》2
 详细分析
-一、上位法依据
-**《中华人民共和国企业所得税法》**第四条规定：企业所得税的税率为25%。第二十八条第二款规定：国家需要重点扶持的高新技术企业，减按15%的税率征收企业所得税。第二十七条规定了可免征、减征企业所得税的情形。
-**《中华人民共和国企业所得税法实施条例》**对减半征收的具体情形作出规定：
-第八十六条：企业从事花卉、茶等饮料作物和香料作物种植、海水养殖、内陆养殖的所得，减半征收企业所得税；
-第八十七条：国家重点扶持的公共基础设施项目，第四年至第六年减半征收企业所得税；
-第八十八条：符合条件的环保节能节水项目，第四年至第六年减半征收企业所得税；
-第九十条：居民企业技术转让所得超过500万元的部分，减半征收企业所得税。
-二、7.5%税率的理论来源
-7.5%税率 = 15%优惠税率 × 50%减半征收。理论上，当居民企业同时满足以下两个条件时，可能产生7.5%的实际税率：
-企业本身适用15%优惠税率（如高新技术企业、西部大开发鼓励类企业等）；
-企业取得的特定所得属于"减半征收"范围。
-三、现行法规对叠加适用的限制
-国税函[2010]157号1第一条对此作出了明确规定：
-第一条第（三）项（现行有效）：居民企业取得实施条例第八十六条、第八十七条、第八十八条和第九十条规定可减半征收企业所得税的所得，是指居民企业应就该部分所得单独核算并依照25%的法定税率减半缴纳企业所得税。即减半征收应以25%法定税率为基础，实际税率为12.5%，而非7.5%。
-第一条第（一）项（现行有效）：居民企业被认定为高新技术企业，同时又处于"两免三减半""五免五半"等定期减免税优惠过渡期的，可以选择依照过渡期适用税率并适用减半征税至期满，或者选择适用高新技术企业的15%税率，但不能享受15%税率的减半征税。
-第一条第（二）项（现行有效）：居民企业被认定为高新技术企业，同时又符合软件生产企业和集成电路生产企业定期减半征收企业所得税优惠条件的，可以选择适用高新技术企业的15%税率，也可以选择依照25%的法定税率减半征税，但不能享受15%税率的减半征税。
-财税[2009]69号2第一条也规定：执行过渡优惠政策及西部大开发优惠政策的企业，在定期减免税的减半期内，可以按照企业适用税率计算的应纳税额减半征税。其他各类情形的定期减免税，均应按照企业所得税25%的法定税率计算的应纳税额减半征税。
-四、7.5%税率可能适用的极少数场景
-根据检索到的法规和实务资料，7.5%税率仅在以下极为有限的过渡期场景中可能适用：
-场景：老高新技术企业过渡期减半征收
-2008年新税法实施初期，2007年3月16日前设立的老高新技术企业处于原"三免三减半"减半期内的，根据国发[2007]39号3和财税[2009]69号2的规定，在过渡优惠政策的减半期内，可以按照企业适用税率计算的应纳税额减半征税。由于老高新技术企业的适用税率为15%，减半征收后实际税率为7.5%。
-但需注意：
-该过渡期政策已到期（原享受定期减免税的企业继续享受到期满为止，新税法自2008年施行，"三免三减半"最长5年减半期，即最晚至2012-2013年左右已结束）；
-国税函[2010]157号第一条第（一）项已明确：选择适用高新技术企业15%税率的，不能享受15%税率的减半征税，进一步限制了7.5%税率的适用。
-五、西部大开发企业的特殊规定
-根据国家税务总局公告2012年第12号4第五条：企业既符合西部大开发15%优惠税率条件，又符合各项税收优惠条件的，可以同时享受。在涉及定期减免税的减半期内，可以按照企业适用税率计算的应纳税额减半征税。这意味着西部大开发鼓励类企业在同时享受15%税率和定期减免税减半期的情形下，理论上可能适用7.5%的实际税率。但需注意该规定仅限于"定期减免税的减半期"，而非实施条例第八十六条至第九十条的"项目所得减半征收"情形。
-策略路径比较
-策略路径	可行性	法律法规依据	关键法律与实务风险
-享受15%优惠税率+项目所得减半征收（7.5%）	</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>❌</t>
-    </r>
+一、关于软件的资产属性
+根据《财政部、国家税务总局关于进一步鼓励软件产业和集成电路产业发展企业所得税政策的通知》（财税[2012]27号）第七条规定3：
+"企业外购的软件，凡符合固定资产或无形资产确认条件的，可以按照固定资产或无形资产进行核算，其折旧或摊销年限可以适当缩短，最短可为2年（含）。"
+这意味着：
+软件既可能作为固定资产核算，也可能作为无形资产核算
+具体如何核算，取决于企业会计政策和该软件是否符合固定资产或无形资产的确认条件
+二、2024年设备、器具一次性扣除政策
+根据《财政部、税务总局关于设备、器具扣除有关企业所得税政策的公告》（财政部、税务总局公告[2023]37号）1：
+"企业在2024年1月1日至2027年12月31日期间新购进的设备、器具，单位价值不超过500万元的，允许一次性计入当期成本费用在计算应纳税所得额时扣除，不再分年度计算折旧。"
+"本公告所称设备、器具，是指除房屋、建筑物以外的固定资产。"
+关键条件：
+时间：2024年1月1日至2027年12月31日期间新购进
+价值：单位价值不超过500万元
+对象：除房屋、建筑物以外的固定资产
+三、软件适用政策分析
+情形一：软件作为固定资产核算
+如果企业将外购软件作为固定资产核算（例如随设备购入、构成设备组成部分的软件，或企业会计政策将软件归入"电子设备"类固定资产），则：
+项目	说明
+是否属于"设备、器具"	是，属于"除房屋、建筑物以外的固定资产"
+能否一次性扣除	可以（300万元≤500万元）
+政策适用期	2024年1月1日至2027年12月31日
+情形二：软件作为无形资产核算
+如果企业将外购软件作为无形资产核算（例如单独购买软件许可、不依附于特定硬件的软件），则：
+项目	说明
+是否属于"设备、器具"	否，无形资产不属于固定资产
+能否一次性扣除	不能
+摊销年限	不得低于10年（一般规定），但可缩短至2年（财税[2012]27号）
+根据《企业所得税法实施条例》第六十五条、第六十七条2：
+"无形资产按照直线法计算的摊销费用，准予扣除。无形资产的摊销年限不得低于10年。"
+但根据财税[2012]27号第七条3：
+"企业外购的软件...其折旧或摊销年限可以适当缩短，最短可为2年（含）。"
+四、实务建议
+审查会计核算方式：首先确认该300万元软件在企业会计上是如何核算的（固定资产还是无形资产）
+如作为固定资产核算：2024年购入的300万元软件，可直接适用一次性扣除政策
+如作为无形资产核算：
+不能适用500万一次性扣除政策
+但可选择缩短摊销年限至2年（需符合财税[2012]27号规定）
+注意事项：
+企业享受一次性扣除或加速折旧/摊销政策，应按规定留存备查相关资料
+会计处理与税务处理可不一致（税法允许税会差异存在），但需准确核算差异
+引用文件
+[1] 财政部、税务总局关于设备、器具扣除有关企业所得税政策的公告
+[2] 中华人民共和国企业所得税法实施条例
+[3] 财政部、国家税务总局关于进一步鼓励软件产业和集成电路产业发展企业所得税政策的通知
+温馨提示：以上分析基于现行有效法规。实务中，建议您根据企业会计政策和具体情况，与主管税务机关沟通确认具体处理方式。如需进一步了解软件作为固定资产还是无形资产核算的标准，建议咨询财务专业人士。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>结论正确但不完整。遗漏了针对海南、横琴的特殊规定，无形资产也可以一次性扣除的情况。是不是AI找到相关的政策37号公告之后就不进一步查找了，导致遗漏了？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>核心结论
+软件通常属于无形资产，不适用"设备、器具"一次性扣除政策。
+2024年企业新购入软件300万元，一般不能一次性税前扣除，而应作为无形资产按不低于10年的期限分期摊销。
+详细分析
+一、一次性扣除政策的适用范围
+根据《财政部、税务总局关于设备、器具扣除有关企业所得税政策的公告》（财政部、税务总局公告[2023]37号）1：
+"企业在2024年1月1日至2027年12月31日期间新购进的设备、器具，单位价值不超过500万元的，允许一次性计入当期成本费用在计算应纳税所得额时扣除。"
+"本公告所称设备、器具，是指除房屋、建筑物以外的固定资产。"
+二、软件的资产属性判定
+根据《中华人民共和国企业所得税法实施条例》2：
+资产类型	定义	典型范围
+固定资产（第五十七条）	企业为生产产品、提供劳务、出租或经营管理而持有的、使用时间超过12个月的非货币性资产	房屋、建筑物、机器、机械、运输工具以及其他与生产经营活动有关的设备、器具、工具等
+无形资产（第六十五条）	企业为生产产品、提供劳务、出租或经营管理而持有的、没有实物形态的非货币性长期资产	专利权、商标权、著作权、土地使用权、非专利技术、商誉等
+软件的税务处理：
+软件属于没有实物形态的非货币性长期资产，通常应归类为无形资产
+因此，软件不属于"设备、器具"的范畴
+一次性扣除政策不适用于软件资产
+三、软件的正确税务处理方式
+根据《企业所得税法实施条例》第六十七条2：
+"无形资产按照直线法计算的摊销费用，准予扣除。
+无形资产的摊销年限不得低于10年。
+作为投资或者受让的无形资产，有关法律规定或者合同约定了使用年限的，可以按照规定或者约定的使用年限分期摊销。"
+软件300万元的税务处理：
+项目	处理方式
+资产类别	无形资产
+摊销方法	直线法
+最短摊销年限	10年
+年摊销额	30万元（300万÷10年）
+四、特殊情况：可缩短摊销年限的情形
+根据《企业所得税法》第三十二条及实施条例第九十八条，以下情形的固定资产可采取缩短折旧年限或加速折旧方法：
+由于技术进步，产品更新换代较快的固定资产
+常年处于强震动、高腐蚀状态的固定资产
+但需注意：上述加速折旧政策适用于固定资产，而非无形资产。
+五、软件摊销年限的特殊规定
+部分情况下，软件可按合同或法律规定年限摊销。例如：
+购买的软件如果有明确的使用许可期限（如3年、5年），可按该期限分期摊销
+但摊销年限仍不得低于法定最低期限
+情形总结
+情形	资产类别	税务处理
+购入独立软件（如ERP系统、办公软件等）	无形资产	按不低于10年分期摊销（或按合同约定年限）
+随硬件一同购入的嵌入式软件	作为固定资产的一部分	随硬件一同计提折旧，可适用一次性扣除（如硬件≤500万元）
+企业自行开发的软件	无形资产	按开发成本资本化，分期摊销
+实务提示
+区分软件与硬件：如软件与硬件一体购入且不可分离，可一并计入固定资产，有机会适用一次性扣除政策。
+合同约定年限：如软件许可合同约定了明确的使用年限（如5年），可按合同约定年限摊销，但需保留合同等相关资料备查。
+研发形成的软件：如软件为企业自主开发形成，相关研发费用可按研发费用加计扣除政策享受75%（或100%）的加计扣除优惠。
+建议咨询主管税务机关：对于软件资产的具体分类和摊销年限，各地执行口径可能存在差异，建议与主管税务机关确认。
+引用法规文件
+[1] 财政部、税务总局关于设备、器具扣除有关企业所得税政策的公告（财政部、税务总局公告[2023]37号）
+[2] 中华人民共和国企业所得税法实施条例（国务院令第512号）
+提醒：以上分析基于现行有效的税收法规文件，具体执行中可能存在地区差异。建议您结合实际情况咨询主管税务机关或专业税务顾问，以获取最新的政策指引。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>结论不正确。将软件归为无形资产，但是在推论里面又提到了软件可能作为固定资产，推论和最终结论有矛盾（这一点327的回答是能答出来的）。并且还是没找到海南、横琴的规定。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>核心结论
+2024年企业新购入软件300万元，不能适用"设备、器具"一次性扣除政策，但可享受最短2年摊销的优惠政策。
+详细分析
+第一步：确定软件的资产属性
+根据《企业所得税法实施条例》1：
+资产类型	定义	典型范围
+固定资产	为生产产品、提供劳务、出租或经营管理而持有的、使用时间超过12个月的非货币性资产	房屋、建筑物、机器、机械、运输工具、设备、器具、工具等
+无形资产	为生产产品、提供劳务、出租或经营管理而持有的、没有实物形态的非货币性长期资产	专利权、商标权、著作权、土地使用权、非专利技术、商誉等
+关键区分点：软件通常属于无形资产（没有实物形态），而非固定资产中的"设备、器具"。
+第二步：一次性扣除政策的适用范围
+根据财政部、税务总局公告[2023]37号2：
+第一条 企业在2024年1月1日至2027年12月31日期间新购进的设备、器具，单位价值不超过500万元的，允许一次性计入当期成本费用在计算应纳税所得额时扣除……
+第二条 本公告所称设备、器具，是指除房屋、建筑物以外的固定资产。
+结论：
+一次性扣除政策仅适用于固定资产中的"设备、器具"
+软件（作为无形资产或特定情形下的固定资产）不属于"设备、器具"范畴
+因此，软件不适用500万元以下一次性扣除政策
+第三步：软件的税务处理政策
+根据财税[2012]27号3第七条：
+企业外购的软件，凡符合固定资产或无形资产确认条件的，可以按照固定资产或无形资产进行核算，其折旧或摊销年限可以适当缩短，最短可为2年（含）。
+这是针对软件的特殊优惠政策：
+会计核算方式	税务处理	摊销/折旧年限
+作为无形资产核算	直线法摊销	最短可为2年（而非一般无形资产的10年）
+作为固定资产核算	直线法折旧	最短可为2年（而非电子设备的3年）
+第四步：2024年购入软件300万元的税务处理
+问题	结论
+能否一次性税前扣除？	不能。软件不属于"设备、器具"，不适用500万元以下一次性扣除政策
+如何处理？	按2年进行摊销（或折旧），每年扣除150万元
+情形对比
+情形	资产类型	300万元是否可一次性扣除	政策依据
+2024年购入软件	无形资产（或固定资产）	不能	财税[2012]27号（最短2年摊销）
+2024年购入电脑/服务器	固定资产-电子设备	可以	公告[2023]37号（一次性扣除）
+2024年购入机器设备	固定资产-机器机械	可以	公告[2023]37号（一次性扣除）
+2024年购入房屋	固定资产-房屋建筑物	不能	公告[2023]37号（明确排除）
+实务提示
+准确区分资产类型：购入软件时应根据会计准则正确判断是作为无形资产还是固定资产核算
+2年摊销是下限：企业可根据软件实际使用年限选择2年或更长的摊销期限
+海南自贸港、横琴合作区的特殊政策：根据财税[2020]31号4和财税[2022]19号5，海南自贸港和横琴粤澳深度合作区对企业新购置的固定资产或无形资产，单位价值不超过500万元的，允许一次性扣除。如果企业在这些特殊区域，软件可能可以一次性扣除
+申报注意事项：享受软件2年摊销优惠时，需在企业所得税年度纳税申报表中正确填报资产折旧、摊销明细
+引用文件
+[1] 中华人民共和国企业所得税法实施条例 国务院令第512号
+[2] 财政部、税务总局公告[2023]37号 关于设备、器具扣除有关企业所得税政策的公告
+[3] 财税[2012]27号 关于进一步鼓励软件产业和集成电路产业发展企业所得税政策的通知
+[4] 财税[2020]31号 关于海南自由贸易港企业所得税优惠政策的通知
+[5] 财税[2022]19号 关于横琴粤澳深度合作区企业所得税优惠政策的通知
+以上分析基于现行法规，具体适用请以主管税务机关认定为准。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>具体分析是正确的，提到了无形资产和固定资产的区分，也找到了横琴海南的政策，但是核心结论里面都没提到。建议结论要根据推论写的完整一些，现在得出的结论有点简单粗暴。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>错（推论对）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>步骤与分析
+1. [优先行动事项]
+核心结论：一般情况下，企业在2024年单独购入价值300万元的软件，在税务处理上通常被认定为“无形资产”，不可以享受500万元以下设备器具的一次性税前扣除政策，但可以享受最短2年的加速摊销优惠。
+例外情形（可一次性扣除）：在以下两种特定情形下，该300万元的软件支出可以实现一次性税前扣除：
+软硬件一体化：该软件与硬件设备一并购入且未单独计价，整体作为“固定资产”核算，且总价值不超过500万元。
+特定区域优惠：企业设立在海南自由贸易港或横琴粤澳深度合作区，这两个区域的税收优惠政策明确允许500万元以下的“无形资产”一次性税前扣除。
+合规风险提示：企业在进行税务申报时，严禁将单独计价并确认为无形资产的软件，人为“包装”或错报为“设备、器具”以套取一次性扣除红利，否则将面临税务稽查、补缴税款及滞纳金的合规风险。
+2. 法律问题拆解与定性
+本咨询涉及以下核心法律问题（管辖地：中国大陆；法律领域：税法/企业所得税；适用法律类别：财政部及税务总局规范性文件）：
+问题一：现行“500万元以下设备、器具一次性扣除政策”的适用客体是否包含无形资产（软件）？（需核实财政部 税务总局公告2023年第37号的适用范围）
+问题二：针对企业外购软件，企业所得税法下是否有专门的加速折旧/摊销规定？（需核实财税〔2012〕27号文）
+问题三：是否存在允许无形资产一次性税前扣除的区域性特殊税收政策？（需核实海南自贸港及横琴粤澳深度合作区相关财税文件）
+3. 具体法律分析
+3.1 一般原则：单独购入的软件作为无形资产，不可适用500万元一次性扣除政策
+实务中，许多企业误以为只要单价不超过500万元的资产均可一次性扣除。根据《财政部 税务总局关于设备、器具扣除有关企业所得税政策的公告》（财政部 税务总局公告2023年第37号）的规定，2024年1月1日至2027年12月31日期间，单位价值不超过500万元的“设备、器具”允许一次性税前扣除。
+然而，该公告第二条明确界定，“设备、器具”是指除房屋、建筑物以外的固定资产。企业单独购入的软件，在会计核算和税务处理上通常被确认为“无形资产”，而非固定资产。因此，单独购入的300万元软件被严格排除在该一次性扣除政策的适用范围之外。
+3.2 替代性税务筹划：软件摊销年限最短可缩短至2年
+虽然不能一次性扣除，但国家对软件产业有专项的税收扶持政策。根据《财政部 国家税务总局关于进一步鼓励软件产业和集成电路产业发展企业所得税政策的通知》（财税〔2012〕27号）第七条的规定，企业外购的软件，凡符合无形资产确认条件的，其摊销年限可以适当缩短，最短可为2年（含）。
+因此，对于这300万元的软件支出，企业在2024年当年最高可按150万元（假设年初购入并按2年期直线法摊销）进行税前扣除，剩余部分在次年扣除。
+3.3 例外情形一：软硬件一体化购入且作为固定资产核算
+如果该软件并非独立运行的商业软件，而是嵌入在某项机器设备中（例如工业控制系统的操作软件），且在采购时与硬件设备一并计价、未单独拆分合同金额。在此情况下，根据会计准则及税务处理惯例，该软硬件整体将被确认为一项“固定资产”。
+只要该项固定资产的总价值（含软件）不超过500万元，即可整体适用财政部 税务总局公告2023年第37号文的规定，在2024年实现一次性税前扣除。
+3.4 例外情形二：特定区域（海南自贸港、横琴）的无形资产专属优惠
+如果贵司设立在特定的国家级经济开发区域，则可能突破上述一般原则：
+海南自由贸易港：根据《财政部 税务总局关于海南自由贸易港企业所得税优惠政策的通知》（财税〔2020〕31号）第一条第（二）项规定，设立在海南自贸港的企业，新购置的无形资产，单位价值不超过500万元的，允许一次性税前扣除。
+横琴粤澳深度合作区：根据《财政部 税务总局关于横琴粤澳深度合作区企业所得税优惠政策的通知》（财税〔2022〕19号）第一条第（二）项规定，设立在横琴的企业同样享受不超过500万元的无形资产一次性税前扣除政策。
+若企业符合上述地域条件，则该300万元的软件（无形资产）可以在2024年全额一次性税前扣除。
+参考文献
+¹ 《财政部 税务总局关于设备、器具扣除有关企业所得税政策的公告》（财政部 税务总局公告2023年第37号），第一条、第二条
+检索日期：2026年3月30日
+一、企业在2024年1月1日至2027年12月31日期间新购进的设备、器具，单位价值不超过500万元的，允许一次性计入当期成本费用在计算应纳税所得额时扣除，不再分年度计算折旧；单位价值超过500万元的，仍按企业所得税法实施条例、《财政部 国家税务总局关于完善固定资产加速折旧企业所得税政策的通知》（财税〔2014〕75号）、《财政部 国家税务总局关于进一步完善固定资产加速折旧企业所得税政策的通知》（财税〔2015〕106号）等相关规定执行。
+二、本公告所称设备、器具，是指除房屋、建筑物以外的固定资产。
+² 《财政部 国家税务总局关于进一步鼓励软件产业和集成电路产业发展企业所得税政策的通知》（财税〔2012〕27号），第七条
+检索日期：2026年3月30日
+七、企业外购的软件，凡符合固定资产或无形资产确认条件的，可以按照固定资产或无形资产进行核算，其折旧或摊销年限可以适当缩短，最短可为2年（含）。
+³ 《财政部 税务总局关于海南自由贸易港企业所得税优惠政策的通知》（财税〔2020〕31号），第一条第（二）项
+检索日期：2026年3月30日
+（二）对在海南自由贸易港设立的企业，新购置（含自建、自行开发）固定资产或无形资产，单位价值不超过500万元（含）的，允许一次性计入当期成本费用在计算应纳税所得额时扣除，不再分年度计算折旧和摊销；新购置（含自建、自行开发）固定资产或无形资产，单位价值超过500万元的，可以缩短折旧、摊销年限或采取加速折旧、摊销的方法。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>回答完全正确，比pro模式回答得好</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>A. 核心结论
+企业在2024年新购入价值300万元的软件，原则上不可以在企业所得税税前进行一次性扣除。
+根据中国现行税法及相关税收优惠政策，单独外购的软件通常作为“无形资产”核算，不属于“设备、器具（除房屋、建筑物以外的固定资产）”的法定保护范畴，因此无法适用500万元以下设备器具一次性扣除政策。针对此类外购软件，企业依法可享受的最大限度税收优惠为缩短摊销或折旧年限，但最短期限不得低于2年 [1]。
+例外情形：若该软件系与特定硬件设备一并购入、不可分离且未单独计价，在会计核算上作为统一的硬件“固定资产”入账（且软硬件总价值不超过500万元），则可随该硬件整体适用一次性税前扣除政策 [2]。
+B. 法律规则与适用分析
+1. “500万元以下设备、器具一次性扣除”的法定边界
+法律规则：根据《财政部 税务总局关于设备、器具扣除有关企业所得税政策的公告》（财政部 税务总局公告2023年第37号）第一条及第二条的明确规定，企业在2024年1月1日至2027年12月31日期间新购进的“设备、器具”，单位价值不超过500万元的，允许一次性计入当期成本费用在计算应纳税所得额时扣除 [2]。该文件对此类资产的外延给出了刚性定义，即“所称设备、器具，是指除房屋、建筑物以外的固定资产” [2]。
+事实适用：固定资产的法定核心特征为具有实物形态（有形资产）。独立购入的计算机软件因缺乏实物形态，在会计与税法认定上均归属于“无形资产”（《企业所得税法实施条例》第六十五条）。因此，独立软件在法律定性上被严格排除在财税〔2023〕37号文所涵摄的有形“固定资产”之外，无法适用一次性扣除红利。
+2. 软件专属的加速折旧/摊销政策（2年期红线）
+法律规则：依据《财政部 国家税务总局关于进一步鼓励软件产业和集成电路产业发展企业所得税政策的通知》（财税〔2012〕27号）第七条规定：“企业外购的软件，凡符合固定资产或无形资产确认条件的，可以按照固定资产或无形资产进行核算，其折旧或摊销年限可以适当缩短，最短可为2年（含）” [1] [3]。
+事实适用：这意味着，即便企业基于某些核算需要将该300万外购软件确认为“固定资产”，其能够适用的特别税务处理规则依然被强制锁定在“缩短折旧年限至2年”，而绝对无法突破底线直接“一次性全额扣除” [1]。在现行年度企业所得税纳税申报表（如A105080《资产折旧、摊销及纳税调整明细表》）的校验逻辑中，“500万元以下设备器具一次性扣除”与“企业外购软件缩短折旧或摊销年限”系完全独立的优惠明细通道，实务中严禁混用。
+3. 嵌入式软件的例外处理（基于“实质重于形式”原则）
+事实适用与定性：若企业购入的300万元软件并非独立运行的系统，而是作为特定机器、机械等有形设备不可或缺的组成部分（如高精度数控机床的内置控制系统软件），且在采购时与硬件未作单独计价或无法物理拆分。
+税务处理：在此特殊情形下，基于“实质重于形式”以及资产不可分割的整体性原则，该部分软件的价值将作为整体硬件设备（固定资产）计税基础的一部分。若该软硬件集合体的设备总价值不超过500万元，则整个系统依法被界定为“设备”，从而可作为一个整体合法适用500万元以下设备器具的一次性税前扣除政策 [2]。
+C. 商业合规与实务建议
+防范错误申报风险：若该300万元软件为独立外购（如ERP系统、财务管理软件、OA办公系统等），财务部门在进行2024年度企业所得税汇算清缴时，必须准确调用《财税〔2012〕27号》的优惠明细，按不低于2年的期限进行直线法摊销/折旧调减 [1]。切勿利用名称模糊在申报表中将其强行并入“500万元一次性扣除”行次，否则极易触发金税四期的底层预警，引发税务稽查、全额补缴当年超额抵扣的税款及滞纳金的重大风险。
+采购合同的架构优化：在未来的资本性支出规划中，若企业进行包含软硬件的综合性系统采购（且商业实质允许），建议在拟定商业采购合同时，将软件与配套的硬件设备合并定义为单一的“智能实体设备”标的，避免将软件金额单列结算。通过前端交易架构的优化固化资产定性，依法最大程度锁定一次性扣除政策带来的当期现金流红利 [2]。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>没有答出海南、横琴的政策。追问地方性政策之后，答出了海南的政策，没答出横琴。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>pro比精简模式更准确</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>德国公司派遣人员，向中国公司提供软件许可及开发项目技术支持，可能涉及的中国企业所得税影响有哪些？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）拆分问题中涉及的业务类型包括软件许可和技术支持服务，先查阅中德税收协定，判断软件许可性质为特许权使用费，根据协定，预提所得税率为10%。技术支持性质为劳务提供，根据常设机构及营业利润条款，应根据人员在境内提供服务时间是否超过183天进一步判断是否构成常设机构以及是否涉税。
+2）查询国内法是否存在相关补充规定，根据国税函〔2009〕507号第五条以及国税函[2010]46号相关规定，中国的做法和第2）步存在一定差异
+3）结合中德税收协定和国内法，梳理各种情形下所得税的不同处理</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="2"/>
+        <family val="3"/>
+        <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> 不可行	国税函[2010]157号第一条第（三）项明确：减半征收应依照25%法定税率	违反减半征收以法定税率为基础的规定，存在补税和滞纳金风险
-享受15%优惠税率+选择25%法定税率减半征收（12.5%）	</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Symbol"/>
-        <family val="2"/>
-      </rPr>
-      <t>✅</t>
+      <t>中德税收协定
+https://www.chinatax.gov.cn/chinatax/n810341/n810770/c1152685/5026956/files/11526851.pdf
+《国家税务总局关于执行税收协定特许权使用费条款有关问题的通知》（国税函〔2009〕507号）
+https://fgk.chinatax.gov.cn/zcfgk/c100012/c5194082/content.html
+《国家税务总局关于税收协定有关条款执行问题的通知》（国税函[2010]46号）
+https://fgk.chinatax.gov.cn/zcfgk/c100012/c5194138/content.html
+《非居民企业所得税核定征收管理办法》（国税发[2010]19号）
+https://fgk.chinatax.gov.cn/zcfgk/c100012/c5200723/content.html</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">需视技术支持服务和许可的相关性，以及构成常设机构情况具体分析：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>若德国公司未在中国境内构成常设机构，且技术支持与软件许可无关：软件许可费适用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 10%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">预提所得税，技术开发支持服务无需缴纳企业所得税。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>若德国公司未在中国境内构成常设机构，但技术支持与软件许可相关：软件许可费适用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 10%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>预提所得税。技术支持服务费视同特许权使用费，一并适用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 10%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">预提所得税
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>若德国公司在中国境内构成常设机构：软件许可费适用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 10%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">预提所得税，技术支持服务费按营业利润据实纳税或核定征收。
+具体分析及政策依据：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">软件许可费（特许权使用费）的企业所得税处理
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>德国公司向中国公司授权使用软件，属于中德税收协定第十二条规定的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>特许权使用费</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">范围。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 
+· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>基本税率：根据中德税收协定第十二条第二款，特许权使用费在其发生的缔约国（中国）征税时，所征税款不应超过特许权使用费总额的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">10%
+· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>国内法衔接：企业所得税法对特许权使用费同样规定</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>10%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">的预提所得税税率
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>无论德国公司是否在中国构成常设机构，软件许可费均按</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>10%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">的税率缴纳预提所得税，由中国公司作为扣缴义务人在支付时代扣代缴。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">技术支持服务费（派遣人员）的企业所得税处理
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>德国公司派遣人员到中国境内提供现场技术指导，属于</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>派遣人员提供劳务</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">的情形，其所得性质为劳务所得，应适用中德税收协定关于营业利润和常设机构的条款。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>判定是否构成常设机构：根据中德税收协定第五条第三款第（二）项，德国公司通过雇员在境内为同一项目或相关联项目提供劳务（包括技术指导），在任何</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个月中连续或累计超过</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>183</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">天的，即构成常设机构。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 
+*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">如果德国公司被判定构成常设机构，技术支持服务费应适用营业利润条款（中德税收协定第七条），按以下方式处理：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>据实申报：能够准确计算归属于常设机构的利润</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>按应纳税所得额</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> × 25%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">计算，分季预缴、年终汇算清缴
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>核定征收：不能如实申报或无法准确核算</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>利润率不低于</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>15%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，应纳税额</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>服务费收入</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> × </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>核定利润率</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> × 25%
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>核定征收的具体方法可以参考国税发</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>[2010]19</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">号。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>但不构成常设机构，技术支持服务费不适用营业利润条款，并不意味着</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不缴纳企业所得税</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">需要进一步区分：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>根据《国家税务总局关于执行税收协定特许权使用费条款有关问题的通知》（国税函〔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>2009</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="1"/>
+        <charset val="134"/>
+      </rPr>
+      <t>〕</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>507</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">号）第五条规定：在转让或许可专有技术使用权过程中，如果技术许可方派人员为该项技术的应用提供有关支持、指导等服务并收取服务费，无论是单独收取还是包括在技术价款中，均应视为特许权使用费，适用税收协定特许权使用费条款的规定。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>这意味着：如果技术支持服务与软件许可属于同一技术转让或许可项目，即使未构成常设机构，技术支持费仍应按特许权使用费处理，适用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>10%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>预提所得税。国税函</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>[2010]46</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>号也印证了上述分析：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>一、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>转让专有技术使用权涉及的技术服务活动应视为转让技术的一部分，由此产生的所得属于税收协定特许权使用费范围。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>但根据协定关于特许权使用费受益所有人通过在特许权使用费发生国设立的常设机构进行营业，并且据以支付该特许权使用费的权利与常设机构有实际联系的相关规定，如果技术许可方派遣人员到技术使用方为转让的技术提供服务，并提供服务时间已达到按协定常设机构规定标准，</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>构成了常设机构的情况下，对归属于常设机构部分的服务收入应执行协定第七条营业利润条款的规定</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，对提供服务的人员执行协定非独立个人劳务条款的相关规定；</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>对未构成常设机构的或未归属于常设机构的服务收入仍按特许权使用费规定处理</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>”</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>常见错误：没有厘清协定和国内税收政策的逻辑关系：
+- 税收协定与中国企业所得税法有不同规定的，依照协定的规定办理。
+- 在实施协定时，对于未经协定明确定义的用语（上下文另有解释的除外），有关缔约国国内法对该用语有解释权。有关用语的定义应适用案件发生时该国有关法律的规定，且税法对相关用语的解释优先于其他法律的解释。</t>
+  </si>
+  <si>
+    <t>核心结论
+德国公司派遣人员向中国公司提供软件许可及开发项目技术支持，可能涉及以下企业所得税影响：
+情形	税务性质	是否构成常设机构	税率	征税方式
+1. 软件许可费	特许权使用费	否	10%（中德协定）	预提所得税（源泉扣缴）
+2. 技术开发服务费	需判断	可能（183天测试）	取决于常设机构认定	如构成常设机构：25%；如不构成：0%
+3. 派遣人员服务费	营业利润	需判断	取决于常设机构认定	同技术开发服务费
+详细分析
+第一步：软件许可费的税务处理
+根据**《企业所得税法实施条例》第二十条**1：
+"特许权使用费所得是指使用或有权使用工业、商业、科学设备，有关工业、商业、科学经验的情报所支付的作为报酬的各种款项"
+根据国税函[2009]507号第三条2：
+"与专有技术有关的特许权使用费一般涉及技术许可方同意将其未公开的技术许可给另一方，使另一方能自由使用，技术许可方通常不亲自参与技术受让方对被许可技术的具体实施，并且不保证实施的结果"
+税务处理：
+所得性质：特许权使用费（被动所得）
+是否构成常设机构：否（特许权使用费不要求在来源国设有常设机构）
+适用税率：10%（中德税收协定）
+征税方式：预提所得税（源泉扣缴）
+应纳税所得额：收入全额（不允许扣除成本）
+第二步：技术开发服务费的税务处理
+技术开发服务需要区分服务性质：
+情形A：技术开发成果归属于德国公司（保留所有权）
+根据国税函[2009]507号第四条2：
+"如果服务提供方提供服务形成的成果属于税收协定特许权使用费定义范围，并且服务提供方仍保有该项成果的所有权，服务接受方对此成果仅有使用权，则此类服务产生的所得，适用税收协定特许权使用费条款的规定"
+税务处理：
+所得性质：特许权使用费
+税率：10%（预提所得税）
+情形B：技术开发成果归属于中国公司（所有权转移）
+根据国税函[2009]507号第六条2：
+"专门从事工程、管理、咨询等专业服务的机构或个人提供的相关服务所取得的款项...应为劳务活动所得"
+税务处理：
+所得性质：劳务所得/营业利润
+是否构成常设机构：需判断（见第三步）
+如构成常设机构：按**25%**税率征收
+如不构成常设机构：0%（但需申报）
+第三步：派遣人员的常设机构判定
+根据国家税务总局公告[2013]19号第一条3：
+"非居民企业派遣人员在中国境内提供劳务，如果派遣企业对被派遣人员工作结果承担部分或全部责任和风险，通常考核评估被派遣人员的工作业绩，应视为派遣企业在中国境内设立机构、场所提供劳务"
+判断因素（满足任一即可能构成常设机构）：
+判断因素	说明
+1. 中国公司向德国公司支付管理费、服务费	表明德国公司通过派遣取得来源于中国的所得
+2. 支付款项超出代垫工资、薪金等费用	表明德国公司保留了利润
+3. 德国公司未将全部费用发放给被派遣人员	保留了一定数额的款项
+4. 德国公司负担的工资薪金未全额在中国缴纳个人所得税	可能存在利润留存
+5. 德国公司确定被派遣人员的数量、任职资格、薪酬标准及工作地点	表明德国公司对人员有实际管理控制
+常设机构判定的时间标准（中德税收协定第五条第三款）4：
+常设机构类型	时间标准
+工程劳务（建筑、安装、装配等）	连续或累计超过6个月
+一般劳务（咨询、技术指导、管理等）	任何12个月内连续或累计超过183天
+第四步：特许权使用费 vs 服务费的区分
+根据国税函[2009]507号第五条2：
+"在转让或许可专有技术使用权过程中如技术许可方派人员为该项技术的使用提供有关支持、指导等服务并收取服务费，无论是单独收取还是包括在技术价款中，均应视为特许权使用费，适用税收协定特许权使用费条款的规定"
+但重要例外：
+"但如上述人员的服务已构成常设机构，则对服务部分的所得应适用税收协定营业利润条款的规定"
+综合税务影响总结
+收入类型	所得性质	常设机构	中国税率	征税方式
+软件许可费	特许权使用费	不要求	10%	预提所得税
+技术开发（成果归德方）	特许权使用费	不要求	10%	预提所得税
+技术开发（成果归中方）	营业利润	需判断	0%或25%	申报或核定征收
+派遣人员服务（不构成PE）	营业利润	否	0%	无需缴税（需申报）
+派遣人员服务（构成PE）	营业利润	是	25%	据实申报或核定征收
+实务操作建议
+合同分拆：建议将软件许可费与技术开发服务费在合同中分别列明，避免被税务机关将全部收入视为特许权使用费
+派遣人员管理：
+如仅代垫工资薪金且不保留利润
+可能不构成常设机构
+如收取服务费或保留利润
+需谨慎评估常设机构风险
+时间控制：劳务活动在任何12个月内尽量控制在183天以内
+避免构成劳务常设机构
+资料准备：
+合同及补充协议
+人员派遣协议
+工作职责说明
+费用支付凭证
+个人所得税完税证明
+申报义务：
+构成常设机构：需办理税务登记和申报
+不构成常设机构：如需享受协定待遇
+仍需按规定备案
+政策依据
+[1] 中华人民共和国企业所得税法实施条例第二十条、第六十五条、第六十六条、第六十七条、第九十一条
+[2] 国家税务总局关于执行税收协定特许权使用费条款有关问题的通知（国税函[2009]507号）
+[3] 国家税务总局关于非居民企业派遣人员在中国境内提供劳务征收企业所得税有关问题的公告（国家税务总局公告[2013]19号）
+[4] 国家税务总局关于印发《〈中华人民共和国政府和新加坡共和国政府关于对所得避免双重征税和防止偷漏税的协定〉及议定书条文解释》的通知（国税发[2010]75号）（第五条常设机构解释）
+[5] 中华人民共和国企业所得税法第三条、第十九条、第三十七条
+[6] 非居民承包工程作业和提供劳务税收管理暂行办法（国家税务总局令第19号）
+[7] 国家税务总局关于发布《非居民纳税人享受协定待遇管理办法》的公告（国家税务总局公告[2019]35号）
+风险提示：以上分析基于现行有效的中国税法规定及税收协定。具体税务处理需结合实际业务安排、合同条款内容及主管税务机关的认定，建议就具体案例与专业税务顾问及主管税务机关沟通确认。由于中德税收协定与中新税收协定条款基本一致，上述分析可参考适用，但具体适用时仍需以中德协定原文为准。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>不太对，引用了中新协定，没有援引中德税收协定。
+在第二步分析了技术开发成果归属，但题目说的是技术支持。
+在综合税务影响总结，表格里派遣人员服务（不构成pe），0%，无需缴税，这里感觉与之前引用的根据国税函[2009]507号第五条相矛盾。
+"在转让或许可专有技术使用权过程中如技术许可方派人员为该项技术的使用提供有关支持、指导等服务并收取服务费，无论是单独收取还是包括在技术价款中，均应视为特许权使用费，适用税收协定特许权使用费条款的规定"</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>核心结论
+德国公司派遣人员向中国公司提供软件许可及开发项目技术支持，可能涉及的中国企业所得税影响主要包括以下几个方面：
+常设机构（PE）判定：若派遣人员在华提供劳务超过183天/12个月，可能构成常设机构
+特许权使用费：软件许可收入可能被认定为特许权使用费，适用10%预提所得税
+技术服务费：若构成常设机构，技术服务所得适用营业利润条款，按25%税率征税
+混合合同处理：需区分特许权使用费与劳务服务费
+分析过程
+第一步：常设机构（PE）的判定
+根据中德税收协定第五条第三款规定1：
+"The furnishing of services, including consultancy services, by an enterprise through employees or other personnel engaged for such purpose, but only if activities of that nature continue (for the same or a connected project) within a Contracting State for a period or periods aggregating more than 183 days within any twelve-month period."
+常设机构判定标准：
+条件	判定标准
+劳务型常设机构	在任何12个月期间，连续或累计超过183天
+工程型常设机构	建筑、装配或安装项目持续超过12个月
+同时，根据国家税务总局公告[2013]19号第一条2，判定派遣行为是否构成机构、场所/常设机构，应考虑以下因素：
+判定因素	说明
+派遣企业对工作结果承担部分或全部责任和风险	核心判定因素
+派遣企业考核评估被派遣人员的工作业绩	核心判定因素
+接收企业向派遣企业支付管理费、服务费	参考因素
+支付款项超出代垫工资等费用	参考因素
+派遣企业保留部分款项	参考因素
+第二步：收入性质的区分——特许权使用费 vs 劳务服务费
+根据国税函[2009]507号3，需区分以下情形：
+1. 特许权使用费的认定
+特征	特许权使用费
+技术许可	许可方同意将其未公开技术许可给另一方使用
+不参与实施	许可方通常不亲自参与技术的具体实施
+不保证结果	许可方不保证实施结果
+成果所有权	服务方保有成果所有权，接受方仅有使用权
+软件许可通常属于特许权使用费范围。
+2. 劳务服务费的认定
+根据国税函[2009]507号第六条，以下款项不属于特许权使用费，应为劳务活动所得：
+单纯货物贸易项下的售后服务报酬
+产品保证期内卖方提供服务的报酬
+专业服务机构提供的工程、管理、咨询等服务
+3. 混合情形的处理
+根据国税函[2009]507号第五条：
+"在转让或许可专有技术使用权过程中如技术许可方派人员为该项技术的使用提供有关支持、指导等服务并收取服务费，无论是单独收取还是包括在技术价款中，均应视为特许权使用费，适用税收协定特许权使用费条款的规定。但如上述人员的服务已构成常设机构，则对服务部分的所得应适用税收协定营业利润条款的规定。"
+第三步：税收影响分析
+根据不同情形，税收影响如下：
+情形一：不构成常设机构
+收入类型	税务处理	税率
+软件许可费	特许权使用费，源泉扣缴	10%（中德协定第十二条）
+技术支持服务费	特许权使用费（与技术许可相关）	10%
+纯劳务服务费	营业利润，仅在企业所在国征税	中国无征税权
+情形二：构成常设机构
+收入类型	税务处理	税率
+归属于常设机构的利润	营业利润，按常设机构利润征税	25%（企业所得税法定税率）
+特许权使用费（与常设机构无关）	仍适用特许权使用费条款	10%
+第四步：中德税收协定关键条款摘要
+根据中德税收协定（2014年签署，2017年生效）1：
+条款	内容	税率/处理
+第五条 常设机构	劳务型常设机构：任何12个月内超过183天	构成PE
+第七条 营业利润	归属于常设机构的利润可在来源国征税	25%
+第十条 股息	持股≥25%：5%；其他：10%	5%或10%
+第十一条 利息	一般情况下	10%
+第十二条 特许权使用费	特许权使用费	10%
+情形分类汇总
+情形	常设机构	软件许可收入	技术支持服务收入	总税负估算
+A	不构成（&lt;183天）	10%预提税	10%预提税（视为特许权使用费）	约10%
+B	构成（≥183天）	10%预提税	25%企业所得税（营业利润）	需分别计算
+C	构成+混合合同	需合理分摊	需合理分摊	按分摊比例计算
+政策依据
+[1] 德意志联邦共和国和中华人民共和国对所得和财产避免双重征税和防止偷漏税的协定（2014年签署，2017年生效）
+[2] 国家税务总局关于非居民企业派遣人员在中国境内提供劳务征收企业所得税有关问题的公告（国家税务总局公告[2013]19号）
+[3] 国家税务总局关于执行税收协定特许权使用费条款有关问题的通知（国税函[2009]507号）
+[4] 中华人民共和国企业所得税法
+[5] 中华人民共和国企业所得税法实施条例
+实务提示
+时间规划：合理规划派遣人员在华时间，避免在12个月内累计超过183天而构成常设机构
+合同分拆：建议将软件许可合同与技术服务合同分开签署，明确各部分的收费标准和服务内容
+费用分摊：如存在混合合同，应准备合理的费用分摊依据，以便税务机关审核
+备案管理：根据国家税务总局公告[2013]19号，符合条件的派遣行为应办理税务登记和备案
+受益所有人认定：德国公司如需享受中德协定优惠待遇，需证明其为相关所得的"受益所有人"
+个人所得税：派遣人员在华工作还涉及个人所得税问题，需另行评估
+增值税：技术服务可能涉及增值税（6%），软件许可不征增值税
+建议咨询主管税务机关：具体适用时，建议结合合同条款和实际情况咨询专业税务顾问或主管税务机关
+以上分析基于现行有效的法规文件，具体执行时请结合实际情况并咨询专业税务顾问或主管税务机关。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>结论正确。遗漏了相关文件，比如国税函[2010]46号文。推导过程中，没有指出核心，即“在实施协定时，对于未经协定明确定义的用语，适用发生时该国国内法的解释”。
+实物提示中，增值税：技术服务可能涉及增值税，软件许可不征增值税。有点画蛇添足，境外向境内提供软件许可，属于境外像境内销售无形资产，征收6%增值税。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>德国公司派遣人员向中国公司提供软件许可及开发项目技术支持的企业所得税影响分析
+核心结论
+德国公司派遣人员向中国公司提供软件许可及开发项目技术支持，可能涉及以下企业所得税影响：（1）软件许可收入按特许权使用费处理，适用中德税收协定限制税率10%1；（2）派遣人员提供技术支持可能构成常设机构（PE），导致相关营业利润在中国缴税2；（3）技术服务费与特许权使用费需要区分处理3。
+分析过程
+第一步：收入性质判定——软件许可属于特许权使用费
+根据《企业所得税法实施条例》第二十条规定，特许权使用费收入是指企业提供专利权、非专利技术、商标权、著作权以及其他特许权的使用权取得的收入4。
+软件许可通常被视为著作权或专有技术的许可使用，其收入性质属于特许权使用费。根据国税函[2009]507号的规定：
+专有技术是指进行某项产品的生产或工序复制所必需的、未曾公开的、具有专有技术性质的信息或资料3
+软件许可属于技术许可方同意将其未公开的技术许可给另一方使用
+第二步：特许权使用费的税务处理
+2.1 国内法规定
+根据《企业所得税法》第三条第三款及第十九条，非居民企业在中国境内未设立机构、场所而取得的特许权使用费所得，以收入全额为应纳税所得额，适用税率为20%，但减按10%税率征收5。
+2.2 中德税收协定优惠
+根据中德税收协定第十二条（特许权使用费）规定，发生于缔约国一方而支付给缔约国另一方居民的特许权使用费，可在该缔约国另一方征税。但来源国（中国）也可征税，税率不超过10%1。
+结论：德国公司向中国公司许可软件使用权取得的特许权使用费，中国有权按10%的税率征收预提所得税。
+第三步：派遣人员提供技术支持——常设机构判定
+这是本案例最关键的税务影响点。
+3.1 常设机构判定标准
+根据国家税务总局公告[2013]19号（关于非居民企业派遣人员提供劳务的公告），判断派遣企业是否构成机构、场所/常设机构，需考虑以下核心因素2：
+基本判定条件：
+判定要素	说明
+责任和风险承担	派遣企业对被派遣人员工作结果承担部分或全部责任和风险
+工作考核	派遣企业通常考核评估被派遣人员的工作业绩
+固定性和持久性	提供劳务的机构、场所具有相对的固定性和持久性
+参考因素（符合任一即可能构成PE）：
+接收企业向派遣企业支付管理费、服务费性质的款项
+接收企业支付的款项超出派遣企业代垫、代付被派遣人员的工资、薪金等费用
+派遣企业保留了部分款项未发放给被派遣人员
+派遣企业负担的被派遣人员工资、薪金未全额在中国缴纳个人所得税
+派遣企业确定被派遣人员的数量、任职资格、薪酬标准及工作地点
+3.2 中德税收协定下的常设机构时间标准
+根据中德税收协定第五条第三款b项规定1：
+通过雇员或其他人员提供劳务（包括咨询服务），如果在任何十二个月内连续或累计超过183天，则构成常设机构。
+3.3 构成常设机构的税务后果
+如果派遣人员提供技术支持构成常设机构：
+德国公司需就归属于该常设机构的营业利润在中国缴纳25%的企业所得税5
+需按照国家税务总局令第19号进行税务登记和申报6
+若账簿不健全，税务机关可按核定利润率方式征收（技术服务通常为15%-30%）7
+第四步：技术服务费与特许权使用费的区分
+根据国税函[2009]507号的明确规定3：
+情形	税务处理
+在转让/许可专有技术过程中，许可方派人员提供支持、指导等服务并收取服务费	视为特许权使用费，无论单独收取还是包括在技术价款中
+上述人员服务已构成常设机构	服务部分所得适用营业利润条款
+服务提供方仅使用专门知识但不转让/许可技术	属于劳务所得，适用营业利润条款
+服务成果所有权归服务提供方，接受方仅有使用权	适用特许权使用费条款
+关键判例参考：德国ThyssenKrupp Stahl公司向马鞍山钢铁转让技术案例中，国家税务总局明确8：
+培训工作属于技术转让性质，执行特许权使用费条款
+技术指导服务如仅指导中方人员使用技术、不直接参与操作，仍为技术转让的组成部分，执行特许权使用费条款
+但服务人员如一个历年内连续或累计停留超过183天，构成常设机构
+情形分类
+情形	条件	企业所得税处理
+A. 纯软件许可	仅许可软件使用权，不派遣人员	按特许权使用费征收10%预提所得税
+B. 软件许可+短期技术支持	派遣人员提供技术支持，但任何12个月内停留≤183天	技术支持费用视为特许权使用费，合并按10%征收
+C. 软件许可+长期技术支持（构成PE）	派遣人员在任何12个月内停留&gt;183天	软件许可仍按10%预提税；归属于常设机构的技术服务利润按25%税率征收企业所得税
+D. 纯技术服务（不涉及软件许可）	仅提供技术支持，不涉及软件许可	若构成常设机构，按营业利润25%征税；若不构成常设机构，中国无征税权
+税务合规要点
+1. 扣缴义务
+根据国家税务总局公告[2017]37号9：
+中国公司作为支付人，负有源泉扣缴义务
+扣缴义务人应自扣缴义务发生之日起7日内申报解缴税款
+到期应支付而未支付的款项，如已计入成本费用并在税前扣除，仍需代扣代缴
+2. 协定待遇享受
+根据国家税务总局公告[2019]35号10：
+德国公司需自行判断是否符合协定待遇条件
+采取"自行判断、申报享受、相关资料留存备查"方式
+需留存税收居民身份证明、合同、"受益所有人"身份证明等资料
+3. 登记备案
+根据国家税务总局令第19号6：
+非居民企业承包工程或提供劳务，应自合同签订之日起30日内办理税务登记
+中国境内发包方需报送《境内机构和个人发包工程作业或劳务项目报告表》
+实务提示
+合同条款设计：建议在合同中明确区分软件许可费用和技术服务费用，以便于税务机关审核和税务处理。
+时间管理：密切关注派遣人员在华停留时间，避免无意中超过183天而构成常设机构。
+资料准备：德国公司应提前准备税收居民身份证明、"受益所有人"证明等资料，以享受协定待遇。
+转让定价风险：若德国公司与中国公司存在关联关系，服务费定价需符合独立交易原则，税务机关有权进行调整。
+建议咨询主管税务机关：由于派遣安排的税务处理较为复杂，具体情形可能需要与主管税务机关沟通确认。
+引用法规
+编号	法规名称
+[1]	《中华人民共和国和德意志联邦共和国对所得和财产避免双重征税和防止偷漏税的协定》
+[2]	《国家税务总局关于非居民企业派遣人员在中国境内提供劳务征收企业所得税有关问题的公告》国家税务总局公告[2013]19号
+[3]	《国家税务总局关于执行税收协定特许权使用费条款有关问题的通知》国税函[2009]507号
+[4]	《中华人民共和国企业所得税法实施条例》国务院令第512号
+[5]	《中华人民共和国企业所得税法》主席令第63号
+[6]	《非居民承包工程作业和提供劳务税收管理暂行办法》国家税务总局令第19号
+[7]	《国家税务总局关于印发〈非居民企业所得税核定征收管理办法〉的通知》国税发[2010]19号
+[8]	《国家税务总局关于德国ThyssenKrupp Stahl公司向马鞍山钢铁股份有限公司热镀锌生产项目转让技术并提供相关服务取得收入适用税收协定规定的批复》国税函[2007]1141号
+[9]	《国家税务总局关于非居民企业所得税源泉扣缴有关问题的公告》国家税务总局公告[2017]37号
+[10]	《国家税务总局关于发布〈非居民纳税人享受协定待遇管理办法〉的公告》国家税务总局公告[2019]35号</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>结论正确。遗漏了相关文件，比如国税函[2010]46号文。推导过程中，没有指出核心，即“在实施协定时，对于未经协定明确定义的用语，适用发生时该国国内法的解释”。
+实务提示中，增值税：技术服务可能涉及增值税，软件许可不征增值税。有点画蛇添足，境外向境内提供软件许可，属于境外向境内销售无形资产，征收6%增值税。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>对，存在推论瑕疵</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>德国公司向中国公司提供软件许可及技术支持的中国企业所得税（EIT）影响分析
+1. [优先行动建议]
+合同拆分与审阅：建议在商业可行的情况下，将“软件许可协议”与“技术开发及支持服务协议”分别签署，或在同一合同中明确区分“特许权使用费”与“纯劳务费”的对价。这有助于防范税务机关将所有费用打包认定为特许权使用费。
+人员在华停留时间追踪（183天红线）：建立严格的内部合规机制，追踪德国派遣人员在任何12个月内在中国境内的停留天数。若为同一或相关联项目累计超过183天，将触发“劳务型常设机构（PE）”风险。
+代扣代缴合规准备：中国公司作为法定扣缴义务人，需在对外支付外汇前，向主管税务机关进行合同备案并代扣代缴企业所得税。
+2. 核心法律问题分析
+问题一：软件许可费的税务定性与适用税率
+法律定性：德国公司向中国公司提供软件许可（即授予版权、专有技术等无形资产的使用权），其收取的费用在《中华人民共和国企业所得税法》及《中德税收协定》下均被界定为“特许权使用费”（Royalties）^^。
+税务影响：对于未在中国境内设立机构、场所的非居民企业，其取得的来源于中国境内的特许权使用费，适用源泉扣缴。法定税率为20%^^，但《企业所得税法实施条例》减按10%征收^^。《中德税收协定》第十二条同样规定特许权使用费的预提税税率不超过10%^^。因此，该部分收入将面临10%的预提企业所得税。
+问题二：技术支持与开发项目费用的税务定性（特许权使用费 vs. 劳务费）
+技术支持与开发费用的税务处理取决于其与软件许可的关联度：
+作为许可的附属服务（特许权使用费）：根据《国家税务总局关于执行税收协定特许权使用费条款有关问题的通知》（国税函〔2009〕507号）第五条，如果德国公司派遣人员是为了该软件/技术的使用提供支持、指导等服务，无论该服务费是单独收取还是包含在技术价款中，均应视为特许权使用费，适用10%的预提所得税^^。
+独立的软件开发服务（营业利润/劳务费）：如果开发项目是根据中国公司需求进行的定制化开发，且知识产权自始归属于中国公司（即不存在技术使用权的让渡），则该费用属于“劳务费”。在《中德税收协定》下，劳务费属于“营业利润”（Business Profits）。除非德国公司在中国构成常设机构，否则中国对该项营业利润没有征税权（即免征中国企业所得税）^^。
+问题三：派遣人员的常设机构（PE）风险及税务影响
+常设机构的触发条件：根据《中德税收协定》第五条，如果德国公司通过其雇员或其他人员在中国境内提供劳务（包括咨询劳务），且该活动（为同一项目或相关联的项目）在任何12个月中连续或累计超过183天，则在中国构成“劳务型常设机构”^^。
+税务影响（若构成PE）：
+税率变化：一旦构成常设机构，归属于该常设机构的劳务收入将不再适用免税或10%的预提税，而是作为境内机构的“营业利润”，适用25%的标准企业所得税税率。
+计税基础：按净利润计征（即收入减去合理成本费用）。如果无法准确核算利润，中国税务机关有权采用“核定利润率”的方式核定应纳税所得额。
+特许权使用费的吸收：如果上述人员的服务构成了常设机构，根据国税函〔2009〕507号规定，原本属于特许权使用费中的“服务部分所得”，将被剥离并适用常设机构的营业利润条款进行征税^^。
+问题四：中国公司的代扣代缴义务
+中国公司作为支付方，负有法定的源泉扣缴义务。在每次支付或到期应支付时代扣代缴税款。若中国公司未履行扣缴义务，将面临税务机关的罚款及滞纳金风险^^。
+3. 法律依据与引用
+《中华人民共和国企业所得税法》
+检索日期：2026-03-30
+第十九条 非居民企业取得本法第三条第三款规定的所得，按照下列方法计算其应纳税所得额：
+（一）股息、红利等权益性投资收益和利息、租金、特许权使用费所得，以收入全额为应纳税所得额；
+（二）转让财产所得，以收入全额减除财产净值后的余额为应纳税所得额；
+（三）其他所得，参照前两项规定的方法计算应纳税所得额。
+《中华人民共和国企业所得税法实施条例》
+检索日期：2026-03-30
+第九十一条 非居民企业取得企业所得税法第二十七条第（五）项规定的所得，减按10%的税率征收企业所得税。
+《国家税务总局关于执行税收协定特许权使用费条款有关问题的通知》（国税函〔2009〕507号）
+检索日期：2026-03-30
+五、在转让或许可专有技术使用权过程中如技术许可方派人员为该项技术的使用提供有关支持、指导等服务并收取服务费，无论是单独收取还是包括在技术价款中，均应视为特许权使用费，适用税收协定特许权使用费条款的规定。但如上述人员的服务已构成常设机构，则对服务部分的所得应适用税收协定营业利润条款的规定。如果纳税人不能准确计算应归属常设机构的营业利润，则税务机关可根据税收协定常设机构利润归属原则予以确定。
+《中华人民共和国政府和德意志联邦共和国政府对所得和财产避免双重征税和防止偷漏税的协定》（中德税收协定）
+注：以下条款原则的精确适用需以官方发布的协定正式文本为准 (This provision requires verification from the official treaty text)。
+第五条（常设机构）：缔约国一方企业通过雇员或雇用的其他人员在缔约国另一方提供劳务，在任何12个月中连续或累计超过183天的，构成常设机构。
+第七条（营业利润）：缔约国一方企业的利润应仅在该国征税，但该企业通过设在缔约国另一方的常设机构进行营业的除外。
+第十二条（特许权使用费）：发生于缔约国一方而支付给缔约国另一方居民的特许权使用费，可以在该缔约国另一方征税。但是，如果特许权使用费受益所有人是缔约国另一方居民，则所征税款不应超过特许权使用费总额的10%。
+4. 风险提示与合规建议
+“同一或相关联项目”的宽泛解释：中国税务机关在计算183天时，往往会将德国公司与中国公司签署的多个看似独立的合同（如分期开发、不同模块的支持）认定为“相关联项目”从而合并计算天数。建议在项目排期时预留充足的安全边际。
+海关与税务的交叉风险：如果软件许可与进口硬件设备相关，该特许权使用费可能同时面临海关的完税价格审查（即是否应计入进口货物完税价格缴纳关税和进口增值税），存在双重征税风险^^。
+受益所有人（Beneficial Owner）判定：德国公司需向中国税务机关证明其为该特许权使用费的“受益所有人”，方可享受《中德税收协定》下的协定待遇，否则可能面临被拒绝适用协定而按国内法从高征税的风险。
+此项查询需要高级别的法律深度，包括战略风险评估和详细的判例法研究。为了确保最高水平的准确性和权威的引用，我们建议使用 Legal Research Pro。
+本人工智能研究功能（“本服务”）提供的信息和材料由人工智能系统生成，仅供参考和研究之用。所提供的内容不旨在也不应被解释为对任何主题的法律或其他专业建议。在未寻求专业法律顾问或其他专业顾问的意见之前，您不应基于本服务提供的任何信息采取或不采取任何行动。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>问题一中，直接将软件许可等同于特许权使用费，应该明确是基于“授予了软件相关的专有技术或版权实际使用权</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">德国公司对华提供软件许可及技术支持之中国企业所得税影响与应对策略备忘录
+A. 执行摘要
+核心发现
+本备忘录旨在评估德国公司向中国公司提供软件许可及派遣人员提供开发项目技术支持所涉及的中国企业所得税（EIT）影响。经全面法律检索与分析，核心发现如下：
+1.	收入定性风险：软件许可费通常被定性为“特许权使用费”，适用10%的预提所得税。若技术支持服务被认定为软件许可的“附属性服务”，税务机关有权将其并入特许权使用费一并征税；若被认定为独立劳务，则在未构成常设机构（PE）的前提下免征中国企业所得税。
+2.	常设机构（PE）触发风险：依据现行《中德避免双重征税协定》，德国公司派员来华提供劳务，若在任何12个月中连续或累计超过183天，将构成“劳务常设机构”。此外，中国税务机关采取“实质重于形式”原则，名义上的“人员派遣”极易被穿透审查为实质性劳务提供。
+3.	核定征收惩罚性税负：一旦构成常设机构且无法准确核算利润，税务机关将按15%至50%的利润率核定征收，叠加25%的法定企业所得税率，将导致极高的实际税负。
+风险评估
+•	税务重新定性风险：高。税务机关对外汇支付中的“服务费”拆分审查极其严格，易触发反避税调查。
+•	常设机构认定风险：高。183天阈值的计算采用“项目合并”与“同批人员不重复计算”原则，且抵离境当日均计入，极易因管理疏忽而超标。
+•	协定待遇被否决风险：中至高。德国公司必须满足“受益所有人”的实质性经营活动测试，否则无法享受协定优惠税率。
+核心建议
+建议德国公司采取“合同实质性拆分与独立定价”结合“严格的在华天数双轨制追踪”策略。在商业合理的前提下，明确界定软件版权许可与常规技术支持的权利边界，并确保派员在华物理停留时间（按项目累计）严格控制在183天安全线内。
+B. 核心问题分析与策略路径
+问题定义与商业背景
+德国公司（非居民企业）向中国公司（居民企业）提供软件许可并派遣人员进行技术支持。此交易模式在税务合规上面临双重挑战：一方面，中国公司作为支付方负有代扣代缴义务；另一方面，德国公司希望实现税务成本最小化。核心法律冲突在于：如何合法地将低税负的“劳务服务”与高税负的“特许权使用费”进行区分，以及如何避免外派人员的活动跨越“常设机构”的法律红线。
+策略路径比较
+策略路径	可行性	法律依据	核心法律与实务风险
+路径A：混合合同统一定价 (将服务费打包进软件许可费)	低	《国家税务总局关于税收协定有关条款执行问题的通知》（国税函〔2010〕46号）第一条 [18]
+全部收入将被定性为特许权使用费，全额适用10%预提所得税，导致服务部分税负无谓增加。
+路径B：人为拆分合同以规避预提税 (将实质为许可的费用包装为高价服务费)	极低	《中华人民共和国企业所得税法》第四十七条 [17]
+极易触发一般反避税调查。税务机关依据“实质重于形式”原则重新定性，追缴税款并加收每日万分之五滞纳金。
+路径C：实质性拆分与PE豁免 (推荐) (独立定价，界定权利边界，严格控制183天阈值)	高	《中德税收协定》第五条 [2]；《非居民纳税人享受协定待遇管理办法》 [13]
+需要极高的人员天数管理精度（抵离境当日计入）；需向主管税务机关提供充分的商业合理性证明及留存备查资料。
+策略路径分析：
+•	路径A（混合合同）虽在执行上最为简便，但会导致德国公司承担不必要的高额预提税，商业效益最差。
+•	路径B（人为拆分）面临极高的行政稽查风险。税务与外汇管理部门的数据联动使得隐匿特许权使用费的操作极易被拦截。
+•	路径C（实质性拆分与PE豁免）是唯一合法且能实现税务优化的路径。其核心在于确保技术支持服务不涉及底层代码或专有技术的转让，且在华停留时间严格受控，从而适用营业利润免税条款。
+C. 适用法律框架
+双边税收协定
+官方来源: 《中华人民共和国和德意志联邦共和国对所得和财产避免双重征税和防止偷漏税的协定》 [2]
+发布机构: 中华人民共和国政府、德意志联邦共和国政府
+条款: 第五条
+原文: "三、“常设机构”一语还包括：...（二）缔约国一方企业通过雇员或雇用的其他人员在缔约国另一方提供劳务，包括咨询劳务，但仅以该性质的活动（为同一或相关联的项目）在任何12个月中连续或累计超过183天的为限。"
+适用性: 确立了德国公司在华提供技术支持是否构成劳务常设机构的183天核心时间阈值。
+企业所得税及反避税法规
+官方来源: 《中华人民共和国企业所得税法》 [17]
+发布机构: 全国人民代表大会
+条款: 第四十七条
+原文: "企业实施其他不具有合理商业目的的安排而减少其应纳税收入或者所得额的，税务机关有权按照合理方法调整。"
+适用性: 赋予税务机关对不合理的“软件许可与技术服务”合同拆分进行重新定性和税务调整的法定权力。
+常设机构与人员派遣认定规则
+官方来源: 《国家税务总局关于非居民企业派遣人员在中国境内提供劳务征收企业所得税有关问题的公告》 [5]
+发布机构: 国家税务总局
+条款: 第一条
+原文: "一、非居民企业（以下统称“派遣企业”）派遣人员在中国境内提供劳务，如果派遣企业对被派遣人员工作结果承担部分或全部责任和风险，通常考核评估被派遣人员的工作业绩，应视为派遣企业在中国境内设立机构、场所提供劳务；如果派遣企业属于税收协定缔约对方企业，且提供劳务的机构、场所具有相对的固定性和持久性，该机构、场所构成在中国境内设立的常设机构。在做出上述判断时，应结合下列因素予以确定：（一）接收劳务的境内企业（以下统称“接收企业”）向派遣企业支付管理费、服务费性质的款项；（二）接收企业向派遣企业支付的款项金额超出派遣企业代垫、代付被派遣人员的工资、薪金、社会保险费及其他费用；..."
+适用性: 确立了“实质重于形式”的审查标准，用于判定德国公司的“人员派遣”是否实质上构成在华提供劳务及常设机构。
+官方来源: 《中华人民共和国政府和新加坡共和国政府关于对所得避免双重征税和防止偷漏税的协定》及议定书条文解释 [4]
+发布机构: 国家税务总局
+条款: 第五条
+原文: "常设机构的概念主要用于确定缔约国一方对缔约国另一方企业利润的征税权。即，按此确定在什么情况下中国税务机关可以对新加坡的企业征税。根据协定第七条的规定，中国不得对新加坡企业的利润征税，除非该企业通过其设在中国的常设机构进行营业。"
+适用性: 该条文解释作为国家税务总局对双边税收协定常设机构条款的通用解释蓝本，明确了按项目计算、同批人员不重复计算的天数计算原则。
+特许权使用费与劳务收入界定
+官方来源: 《国家税务总局关于税收协定有关条款执行问题的通知》（国税函〔2010〕46号） [18]
+发布机构: 国家税务总局
+条款: 第一条
+原文: "转让专有技术使用权涉及的技术服务活动应视为转让技术的一部分，由此产生的所得属于税收协定特许权使用费范围。"
+适用性: 明确了附属于软件许可（专有技术）的技术支持服务费不能作为独立劳务免税，而必须并入特许权使用费征收预提税。
+协定待遇享受与受益所有人规则
+官方来源: 《国家税务总局关于税收协定中"受益所有人"有关问题的公告》 [12]
+发布机构: 国家税务总局
+条款: 第二条
+原文: "二、判定需要享受税收协定待遇的缔约对方居民（以下简称“申请人”）“受益所有人”身份时，应根据本条所列因素，结合具体案例的实际情况进行综合分析。一般来说，下列因素不利于对申请人“受益所有人”身份的判定：（一）申请人有义务在收到所得的12个月内将所得的50%以上支付给第三国（地区）居民，...（二）申请人从事的经营活动不构成实质性经营活动。实质性经营活动包括具有实质性的制造、经销、管理等活动。..."
+适用性: 规定了德国公司申请享受《中德税收协定》特许权使用费优惠税率必须通过的实质性经营活动等综合因素测试。
+官方来源: 《非居民纳税人享受协定待遇管理办法》 [13]
+发布机构: 国家税务总局
+条款: 第二十一条
+原文: "主管税务机关在后续管理过程中，发现需要适用税收协定主要目的测试条款或国内税收法律规定中的一般反避税规则的，适用一般反避税相关规定。"
+适用性: 确立了非居民企业享受协定待遇的“自行判断、申报享受、相关资料留存备查”机制及税务机关的事后反避税监管权。
+核定征收规则
+官方来源: 《非居民企业所得税核定征收管理办法》 [15]
+发布机构: 国家税务总局
+条款: 第四条
+原文: "第四条 非居民企业因会计账簿不健全，资料残缺难以查账，或者其他原因不能准确计算并据实申报其应纳税所得额的，税务机关有权采取以下方法核定其应纳税所得额。（一）按收入总额核定应纳税所得额：适用于能够正确核算收入或通过合理方法推定收入总额，但不能正确核算成本费用的非居民企业。计算公式如下：应纳税所得额=收入总额×经税务机关核定的利润率..."
+适用性: 规定了当德国公司在华构成常设机构且无法准确核算利润时，税务机关强制适用核定利润率征税的法律依据。
+D. 案例法与执法实践分析
+在中国国际税收争议解决的特殊环境下，关于非居民企业常设机构认定及特许权使用费定性的争议极少进入公开的法院诉讼阶段。纳税人通常在税务稽查或相互协商程序（MAP）阶段与税务机关达成补税和解，以避免漫长的复议前置程序和高昂的滞纳金 [7]。因此，本节重点分析具有高度指导意义的官方行政稽查案例。
+典型行政稽查案例分析
+北京地税局对外资车企“劳务常设机构”穿透案
+•	案件背景：甲国母公司B向其在华合资企业A派遣了多名雇员，负责技术指导和售后服务。B公司主张其派遣的单个员工在华时间均不足183天，且工资在境外发放，因此不构成常设机构 [6][8]。
+•	税务机关裁决：北京税务机关成立专项调查组，依据“实质重于形式”原则认定境外B公司为真实雇主。税务机关将所有外派员工为同一项目在12个月内的在华停留时间进行累计合并计算，认定总时间超过183天，最终判定B国母公司外派员工在华构成19个“劳务型常设机构” [6][8]。
+•	案件结果：B公司被要求补缴企业所得税及个人所得税1771.03万元，加收滞纳金549.85万元，共计补缴2320.88万元 [6][8]。
+•	关联性与启示：该案明确展示了中国税务机关在计算183天阈值时，坚决采用“项目合并计算”而非“单人分散计算”的执法口径。德国公司若试图通过多批次、短时间派员来规避PE风险，在现行稽查手段下已不可行。
+宁夏宁东国税局非居民企业常设机构认定案
+•	案件背景：境外机构通过人为拆分中国境内的工程作业与技术指导业务，将一项整体服务拆分成几个独立的派遣与服务合同，试图规避常设机构的时间门槛 [9]。
+•	税务机关裁决：税务机关在反避税调查中，运用“实质重于形式”原则，将几个分散的合同依据其商业上的关联性、作业地点和时间上的一致性，认定各个独立合同实质是一项整体合同的组成部分，从而合并计算在华作业时间，成功判定其构成常设机构并征税 [9]。
+•	关联性与启示：此案表明，人为的“合同拆分”不仅无法规避常设机构风险，反而会触发税务机关的反避税合并审查。德国公司在提供软件许可与技术支持时，若服务具有高度连贯性，将被视为“同一或相关联的项目”。
+E. 详细法律分析
+核心争议一：收入性质的界定（特许权使用费 vs. 劳务收入）
+A. 适用法律标准
+在跨境软件交易中，收入定性是决定税负的核心。根据《国家税务总局关于税收协定有关条款执行问题的通知》（国税函〔2010〕46号）第一条规定，转让专有技术使用权涉及的技术服务活动应视为转让技术的一部分，由此产生的所得属于税收协定特许权使用费范围 [18]。此外，《企业所得税法》第四十七条赋予了税务机关对不具有合理商业目的的安排进行调整的权力 [17]。
+B. 事实应用与分析
+德国公司向中国公司提供软件许可及开发项目技术支持，其收入定性取决于技术支持的实质内容与权利归属：
+4.	纯劳务收入的界定：如果德国公司仅提供常规的软件售后维护、系统环境配置、不涉及底层代码修改的排障服务，且未向境内企业转让或许可任何未公开的专有技术，该部分技术支持费应界定为劳务收入。在未构成常设机构的情况下，无需在中国缴纳企业所得税。
+5.	附属性服务的吸收原则：如果德国公司许可了软件底层算法（专有技术），同时派工程师提供开发项目的技术指导，以确保该算法能成功嵌入中国公司的系统中。此时，依据国税函〔2010〕46号文 [18]，即使技术指导费在合同中单独列示，也会被税务机关视为技术许可的不可分割部分（即“主从原则”），合并计入特许权使用费，全额征收10%的预提所得税。
+C. 潜在抗辩与税务机关立场
+德国公司可能主张《技术支持协议》是一份独立的商业合同，具有独立的定价。然而，税务执法实践表明，税务机关会穿透合同名称，审查境内企业支付费用的根本目的是否是为了获得软件无形资产的使用权。若拆分缺乏合理商业目的，税务机关将依据《企业所得税法》第四十七条实施反避税调整 [17]。
+核心争议二：劳务常设机构（PE）的触发与183天计算规则
+A. 适用法律标准
+根据《中德税收协定》第五条第三款第（二）项，缔约国一方企业通过雇员在缔约国另一方提供劳务，仅以该性质的活动（为同一或相关联的项目）在任何12个月中连续或累计超过183天的为限，构成常设机构 [2]。同时，《国家税务总局关于非居民企业派遣人员在中国境内提供劳务征收企业所得税有关问题的公告》（2013年第19号）第一条确立了判定真实雇主的“实质重于形式”标准 [5]。
+B. 事实应用与分析
+德国公司派遣人员来华提供技术支持，面临极高的PE触发风险，具体体现在两个维度：
+6.	“名义派遣”的穿透审查：若德国公司与中国公司签署《人员派遣协议》，主张人员受雇于中国公司。税务机关将依据19号公告 [5] 审查资金流（中国公司支付的款项是否包含利润加成）、控制流（谁决定薪酬和考核）以及风险流。若德国公司仍对工作成果负责或保留部分款项，将被认定为在华提供劳务的“真实雇主”。
+7.	183天阈值的严苛计算：依据国税发〔2010〕75号文的解释精神 [4]，183天的计算实行“按项目计算、同批人员不重复计算”原则。这意味着：
+•	滚动测试：183天是在“任何12个月”内滚动计算，而非单一自然年度。
+•	项目合并：如果开发项目历经数年，只要在某一个12个月期间内派员超过183天，税务机关将判定该企业在整个项目期间均构成常设机构 [4]。
+•	抵离境当日计入：在企业所得税层面，遵循物理存在原则，外派人员抵境和离境的当日（即使不足24小时）均须计入项目存续天数。
+核心争议三：构成常设机构后的极端税负后果（核定征收）
+A. 适用法律标准
+根据《非居民企业所得税核定征收管理办法》第四条，非居民企业因资料残缺难以查账等原因不能准确计算应纳税所得额的，税务机关有权按收入总额核定应纳税所得额 [15]。
+B. 事实应用与分析
+一旦德国公司的技术支持活动因超过183天被认定为常设机构，且德国公司无法向中国税务机关提供符合中国会计准则的完整账簿来准确核算该在华项目的成本费用，税务机关将强制启动核定征收程序 [15]。
+•	若被界定为“设计和咨询劳务”，法定核定利润率为15%-30% [15]。实际税负率 = 收入总额 × 30% × 25% = 7.5%。
+•	若被穿透认定为“管理服务”，核定利润率将飙升至30%-50% [15]。实际税负率最高可达总收入的12.5%。
+•	最坏情况（境内外划分失败）：若德国公司主张部分技术支持在德国远程完成，但无法提供详尽的工时单（Timesheet）证明，税务机关有权视同其提供的服务全部发生在中国境内，对100%的合同收入全额征税。
+核心争议四：协定优惠待遇的申请与“受益所有人”资格
+A. 适用法律标准
+根据《国家税务总局关于税收协定中"受益所有人"有关问题的公告》（2018年第9号）第二条，申请人从事的经营活动必须构成实质性经营活动，否则将面临不利于“受益所有人”身份的判定 [12]。《非居民纳税人享受协定待遇管理办法》第二十一条规定了税务机关的后续反避税管理权 [13]。
+B. 事实应用与分析
+针对被界定为“特许权使用费”的软件许可收入，德国公司若要享受《中德税收协定》的限制税率（一般为10%，特定设备为6%），必须具备“受益所有人”资格。
+•	实质性测试：德国公司不能仅是持有软件版权的“空壳公司”。依据9号公告 [12]，其必须在德国当地履行与收取特许权使用费相匹配的功能（如研发、技术维护），并承担相应风险。
+•	资金流向审查：若德国公司在收到中国公司支付的特许权使用费后，12个月内将50%以上的资金转付给第三国居民（如避税天堂的母公司），将被直接否定受益所有人资格 [12]。
+•	程序合规：现行机制下，德国公司无需事前审批，但必须填写《信息报告表》交由中国公司扣缴申报，并自行归集留存备查资料以应对税务机关的后续抽查 [13]。
+F. 缺失事实与信息缺口
+为提供绝对确定的税务计算与最终定性，本备忘录的分析基于现有信息。以下关键事实的缺失可能实质性改变法律结论：
+8.	合同定价与拆分细节：软件许可费与技术支持服务费是否在同一份合同中？是否具有独立、公允的商业定价依据？
+9.	技术支持的具体内容：德国人员在华提供的技术支持，是仅涉及常规的系统安装与排障，还是涉及软件底层源代码的二次开发与专有技术传授？
+10.	知识产权归属：开发项目完成后，新形成的技术成果或软件著作权归属于德国公司还是中国公司？
+11.	人员在华天数与批次安排：德国公司计划派遣多少名员工？预计的首次抵华日期与项目最终交付日期跨度多长？单次停留与累计停留的具体天数预估？
+12.	资金流向与德国公司实质：德国公司是否为该软件的初始研发者？其收到款项后是否有义务支付给集团内的其他实体？
+G. 实践影响与合规要求
+源泉扣缴与备案义务
+•	中国公司的扣缴责任：中国公司作为支付方，负有法定的代扣代缴义务。在对外支付特许权使用费或服务费前，必须向主管税务机关进行税务备案。若德国公司未提供完整的《信息报告表》及相关证明，中国公司绝不能擅自适用税收协定优惠税率，否则将承担少缴税款的连带法律责任。
+•	外汇与税务联动拦截：中国公司在银行办理付汇时，税务机关与外汇局的数据比对系统会自动审查“服务费”名义下的支付是否隐匿了特许权使用费。
+人员停留天数追踪（双轨制管理）
+德国公司必须建立极其精确的在华天数追踪系统。由于企业所得税（PE判定）与个人所得税（居住天数判定）的计算口径完全不同，必须实施“双轨制”台账：
+•	PE防范台账：记录项目组任何成员在华的绝对物理天数。只要当天有人在境内（含抵离境当日的半天），该日即计入项目天数（+1）。警戒线必须设置在160天左右，以预留缓冲期。
+H. 战略建议
+基于上述法律与实务分析，为实现税务成本最小化并确保合规，建议采取以下分级策略：
+短期交易架构与合同建议
+13.	实施实质性的合同拆分：若商业上具有合理性，强烈建议将“软件许可协议”与“技术支持服务协议”分别签署。在服务协议中，明确声明“本服务不涉及任何专有技术、专利或版权的转让与排他性许可”，以阻断税务机关依据国税函〔2010〕46号文 [18] 将服务费并入特许权使用费的路径。
+14.	建立公允的独立定价机制：服务费的定价必须符合独立交易原则，需备齐工时单（Timesheet）、人员级别费率表等证明材料，防范反避税审查。
+15.	完善“受益所有人”证据链：德国公司应立即着手准备在德国具有实质性经营活动（研发人员雇佣记录、办公场所租赁合同）的证明材料，以备中国税务机关抽查 [12][13]。
+中长期人员派遣与PE防范建议
+16.	优化派员批次（集中兵力策略）：鉴于“同批人员不重复计算”原则，德国公司应尽量采取“集中兵力、短期突击”的策略。例如，一次性派5名工程师集中工作30天（计为30天），绝对避免将5名工程师分5个批次单独来华（累计将达150天，逼近183天红线）。
+17.	切断“真实雇主”认定因素：若采用人员派遣模式，必须确保中国公司对被派遣人员的工作结果承担全部责任和风险，且德国公司不应从中国公司支付的派遣费中截留利润或收取管理费，以规避19号公告 [5] 的穿透审查。
+18.	严格的工时与地点隔离：要求德国工程师严格区分“在华现场工作时间”与“德国远程工作时间”，并保留详尽的系统登录日志与邮件记录。一旦发生PE争议，此举可防止税务机关将100%的合同收入视同境内劳务收入进行极端核定征收 [15]。
+I. 结论
+德国公司向中国公司提供软件许可及技术支持，面临着复杂的中国企业所得税定性与常设机构触发风险。若处理不当，不仅软件许可费将面临10%的预提所得税，其技术支持服务费也极易被税务机关依据“主从原则”合并征收预提税，或因外派人员在华超过183天而触发“劳务常设机构”，进而被适用惩罚性的核定利润率征收25%的企业所得税。
+为有效管控上述风险，德国公司与中国公司应立即采取行动：在交易前端，通过实质性的合同拆分与公允定价，清晰界定版权许可与常规劳务的边界；在项目执行端，建立严格的“双轨制”人员天数追踪台账，坚决将项目组在华物理停留时间控制在183天以内；在合规申报端，妥善准备并留存德国公司作为“受益所有人”的实质性经营证据。通过上述综合筹划，方能在合法合规的前提下，最大程度地降低跨境交易的整体税务摩擦成本。
+</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="2"/>
+        <family val="1"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> 可行	国税函[2010]157号第一条第（二）项：可选择依照25%法定税率减半征税	需放弃15%优惠税率对该部分所得的适用，选择25%减半
-过渡期老高新技术企业15%税率减半（7.5%）	</t>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>The information and materials provided by this AI-powered research function (“the Service”) are generated by an artificial intelligence system and are for informational and research purposes only. The content provided is not intended to be, and should not be construed as, legal or other professional advice on any subject matter. You should not act or refrain from acting based on any information provided by the Service without seeking professional legal counsel, or other professional counsel.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>回答和分析都正确</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>分析结论
+德国公司向中国公司提供软件许可并派遣人员提供技术支持，可能涉及的中国企业所得税影响可分为以下几个层面，需逐一分析。
+一、软件许可费——特许权使用费预提所得税
+1. 收入定性
+软件许可费通常被认定为特许权使用费。《企业所得税法实施条例》第二十条规定5：
+"企业所得税法第六条第（七）项所称特许权使用费收入，是指企业提供专利权、非专利技术、商标权、著作权以及其他特许权的使用权取得的收入。"
+《国家税务总局关于执行税收协定特许权使用费条款有关问题的通知》（国税函[2009]507号） 第三条进一步明确2：
+"与专有技术有关的特许权使用费一般涉及技术许可方同意将其未公开的技术许可给另一方，使另一方能自由使用，技术许可方通常不亲自参与技术受让方对被许可技术的具体实施，并且不保证实施的结果。被许可的技术通常已经存在，但也包括应技术受让方的需求而研发后许可使用并在合同中列有保密等使用限制的技术。"
+软件许可使中国公司获得使用权但德方保留所有权，其费用性质属于特许权使用费。
+2. 税率
+根据《企业所得税法》第三条第三款及第四条4，非居民企业来源于中国境内的特许权使用费所得，法定税率为20%；实施条例第九十一条规定减按**10%**征收5。
+根据**《中华人民共和国政府和德意志联邦共和国政府关于对所得避免双重征税和防止偷漏税的协定》，特许权使用费的协定限制税率通常为10%。中国公司作为支付人应以10%**的税率代扣代缴预提所得税。
+二、派遣人员技术支持——常设机构（PE）风险
+这是本交易中最复杂也最关键的企业所得税问题。
+1. 是否构成机构、场所/常设机构
+《国家税务总局关于非居民企业派遣人员在中国境内提供劳务征收企业所得税有关问题的公告》（国家税务总局公告[2013]19号） 第一条1：
+"非居民企业派遣人员在中国境内提供劳务，如果派遣企业对被派遣人员工作结果承担部分或全部责任和风险，通常考核评估被派遣人员的工作业绩，应视为派遣企业在中国境内设立机构、场所提供劳务；如果派遣企业属于税收协定缔约对方企业，且提供劳务的机构、场所具有相对的固定性和持久性，该机构、场所构成在中国境内设立的常设机构。"
+判定时需结合以下因素1：
+（一）中国公司向德国公司支付管理费、服务费性质的款项；
+（二）中国公司向德国公司支付的款项超出代垫代付被派遣人员工资等费用；
+（三）德国公司未将中国公司支付的相关费用全部发放给被派遣人员，而是保留了一定数额；
+（四）德国公司负担的被派遣人员工资未全额在中国缴纳个人所得税；
+（五）德国公司确定被派遣人员的数量、任职资格、薪酬标准及在中国境内的工作地点。
+在您描述的情形中，德国公司派遣人员为中国公司提供软件开发项目技术支持，通常意味着德国公司对工作结果承担一定责任和风险，很可能被认定为在中国境内设立机构、场所。
+2. 劳务型常设机构的天数门槛
+根据中德税收协定（以及《国家税务总局关于税收协定执行若干问题的公告》公告[2018]11号的统一解释3），如果派遣人员在任何十二个月中连续或累计超过183天在中国境内提供劳务，则构成常设机构。
+构成常设机构的关键天数阈值：183天（在任何十二个月中连续或累计）
+3. 构成常设机构的税务后果
+如果德国公司被认定为在中国构成常设机构：
+税率：归属于常设机构的利润按**25%**的企业所得税税率征税（不再是10%的预提税率）4
+计税基础：以净收入（收入减除成本费用）为应纳税所得额，而非总收入
+申报方式：据实申报，或由税务机关核定征收1
+4. 未构成常设机构的情况
+如果派遣人员在任何十二个月中未超过183天，且不构成其他类型的常设机构，则根据税收协定营业利润条款，德国公司在中国不承担企业所得税纳税义务（营业利润仅在居民国征税）。
+三、软件许可与技术支持服务交织的处理
+国税函[2009]507号第五条对"许可+服务"交织的情形给出了明确的处理规则2：
+"在转让或许可专有技术使用权过程中如技术许可方派人员为该项技术的使用提供有关支持、指导等服务并收取服务费，无论是单独收取还是包括在技术价款中，均应视为特许权使用费，适用税收协定特许权使用费条款的规定。
+但如上述人员的服务已构成常设机构，则对服务部分的所得应适用税收协定营业利润条款的规定。"
+这一规定的逻辑链条如下：
+情形	服务费税务处理
+伴随许可的技术支持服务，未构成常设机构	服务费视为特许权使用费，按**10%**预提所得税（总额征收）
+伴随许可的技术支持服务，已构成常设机构	服务部分按营业利润处理，归属于常设机构的利润按**25%**征收（净额征收）
+这意味着：
+如果技术支持服务单独收费且金额可区分，在未构成常设机构时，该部分费用也按特许权使用费10%征税
+如果构成常设机构，服务费需从特许权使用费中分离出来，按25%税率对净利润征税
+如果纳税人不能准确计算归属常设机构的利润，税务机关有权核定2
+四、综合影响分析框架
+税务影响维度	具体分析
+软件许可费	特许权使用费，中国公司按10%代扣代缴预提所得税
+技术支持服务费（未构成PE）	视为特许权使用费的一部分，按10%预提所得税
+技术支持服务费（构成PE）	服务部分按营业利润处理，以净收入25%征企业所得税
+混合合同	如合同未拆分许可费与服务费，可能被税务机关整体认定为特许权使用费或要求拆分
+增值税	软件许可费及服务费可能还涉及增值税（此为另一税种，需另行分析）
+五、实务操作建议
+合同设计：建议将软件许可和技术支持服务在合同中明确拆分，分别约定费用金额，以便在税务处理时有据可依。
+控制派遣天数：如希望避免构成常设机构，应将派遣人员在华提供技术支持的时间控制在任何十二个月中不超过183天。同时需注意，这不仅仅是单个人天数的计算，同一项目多人的天数可能被累计3。
+派遣安排的实质审查：根据公告[2013]19号第五条1，税务机关将重点审核：派遣合同、管理规定、支付情况、个人所得税申报等，以确定派遣安排的经济实质。
+源泉扣缴义务：中国公司作为支付方，对特许权使用费负有源泉扣缴义务（应在支付或到期应支付时扣缴税款，并在7日内缴入国库）4。未依法扣缴的，可能承担补扣责任。
+税收协定待遇：德国公司享受中德税收协定待遇（如10%优惠税率），需按照《国家税务总局关于发布〈非居民纳税人享受协定待遇管理办法〉的公告》（国家税务总局公告[2019]35号）的规定，自行判断是否符合条件并在申报时提交相关资料。
+关注软件开发部分的特殊性：如果技术支持涉及新软件的定制开发而非对已有软件的使用提供支持，开发服务的所得可能不属于特许权使用费，而应按劳务/营业利润处理，需结合具体合同条款和业务实质判断。
+上位法依据
+本分析所引用的上位法包括：
+《中华人民共和国企业所得税法》（2018修订版）
+《中华人民共和国企业所得税法实施条例》（国务院令[2007]512号）
+《中华人民共和国政府和德意志联邦共和国政府关于对所得避免双重征税和防止偷漏税的协定》（及议定书）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>化妆品生产企业2025年将成本为8万，市场零售价为10万的自产化妆品用于广告宣传，会计入账广告费用8万，该事项在2025年企业所得税汇算清缴的时候需要进行哪些纳税调整呢？假设先不考虑增值税影响。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1）解读该问题，分析该填报可能涉及视同销售和广宣费限额纳税调整的问题。
+2）检索企业所得税视同销售法规及其填表规则，定位到《国家税务总局关于企业处置资产所得税处理问题的通知》（国税函[2008]828号）、国家税务总局公告[2016]80号和国家税务总局关于修订企业所得税年度纳税申报表有关问题的公告 （国家税务总局公告[2019]41号），确定视同销售的填表处理。
+3）检索广宣费相关企业所得税规定，定位到企业所得税法实施条例及《财政部、税务总局关于广告费和业务宣传费支出税前扣除有关事项的公告》（财政部、税务总局公告[2025]16号）对于一般扣除限额15%的规定，以及对化妆品生产企业的特殊规定30%限额。
+4）结合上述规定以及企业所得税申报表的表单及填报规则，提供纳税调整思路</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">《国家税务总局关于企业处置资产所得税处理问题的通知》（国税函[2008]828号）
+https://fgk.chinatax.gov.cn/zcfgk/c100012/c5193979/content.html
+国家税务总局关于企业所得税有关问题的公告（国家税务总局公告[2016]80号）
+https://fgk.chinatax.gov.cn/zcfgk/c100012/c5194698/content.html
+国家税务总局关于修订企业所得税年度纳税申报表有关问题的公告 （国家税务总局公告[2019]41号）
+https://fgk.chinatax.gov.cn/zcfgk/c100012/c5194895/content.html
+《财政部、税务总局关于广告费和业务宣传费支出税前扣除有关事项的公告》（财政部、税务总局公告[2025]16号）
+https://fgk.chinatax.gov.cn/zcfgk/c102416/c5246328/content.html
+国家税务总局关于优化企业所得税年度纳税申报表的公告（国家税务总局公告[2025]1号）
+https://fgk.chinatax.gov.cn/zcfgk/c100012/c5237968/content.html
+企业所得税法实施条例
+https://fgk.chinatax.gov.cn/zcfgk/c100010/c5194417/content.html
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">对于您将自产化妆品用于广告宣传的行为，在2025年度企业所得税汇算清缴时，需要进行以下两项核心纳税调整：第一步是“视同销售”调整，第二步是“广告费限额”调整（假设先不考虑增值税等税费）。
+第一步：视同销售纳税调整
+由于将自产货物用于广告宣传，资产所有权发生了转移，根据国税函[2008]828号及国家税务总局公告[2016]80号，应作视同销售处理，按化妆品的公允价值确定销售收入，该事项在会计上仅确认了8万元销售费用，而未确认收入，会产生税会差异，需要进行调整。
+视同销售调整（A105010表）
+- 视同销售收入（按市场零售价10万）：纳税调增10万
+- 视同销售成本（按成本8万）：纳税调减8万
+- 视同销售净影响：调增应纳税所得额 2万
+第二步：广告费和业务宣传费限额纳税调整
+会计上已将产品的成本计入了“销售费用”，但经第一步视同销售调整后，税法认可的广告费增加，可能涉及扣除限额的纳税调整。
+· 确认税法认可的广告费金额：用于广告宣传的视同销售行为，税法允许扣除的广告费基础应为产品的公允价值10万元（假设不考虑增值税影响）。而您会计上确认的广告费是8万元，两者存在2万元的差异。根据国家税务总局公告[2019]41号，《A105000纳税调整项目明细表》填报说明：第30行“其他”中，填报因视同销售纳税调整后，对应支出的会计处理与税收规定差异需调整的金额。在此步骤计算限额时，应直接采用税法认可的10万元作为该笔业务的广告费支出。并将2万元差额填写在A105000第30行“其他”中。
+· 计算扣除限额：
+  1. 确定销售收入基数：根据规定，广告费扣除限额的计算基础包括主营业务收入、其他业务收入以及视同销售收入。您因该笔业务已在第一步确认了10万元视同销售收入，这10万元需加到您原有的销售收入中，用以计算扣除限额。
+  2. 适用扣除比例：若企业属于化妆品制造或销售企业，根据财政部、税务总局公告[2025]16号，广告费和业务宣传费支出不超过当年销售（营业）收入30% 的部分，准予扣除，超过30%的部分可以在以后纳税年度结转扣除。广告费的填写应在《A105060 广告费和业务宣传费跨年度纳税调整明细表》中体现。
+</t>
+  </si>
+  <si>
+    <t>常见错误：“视同销售”调整会遗漏“其他”项的调整，可能没有检索到国家税务总局公告[2019]41号或无法/遗漏读取企业所得税申报表的填报规则</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">核心结论
+化妆品生产企业将自产化妆品用于广告宣传，在2025年企业所得税汇算清缴时，主要涉及两项纳税调整：视同销售纳税调整和广告宣传费税前扣除限额调整。
+分析过程
+一、视同销售纳税调整
+1. 为什么需要视同销售？
+根据《企业所得税法实施条例》第二十五条规定，企业将货物用于广告等用途的，应当视同销售货物2。同时，《国家税务总局关于企业处置资产所得税处理问题的通知》（国税函[2008]828号）第二条明确：企业将资产用于市场推广或销售的，因资产所有权属已发生改变，应按规定视同销售确定收入3。
+本案例中，企业将自产化妆品用于广告宣传，属于"用于市场推广或销售"的情形，必须进行视同销售处理。
+2. 视同销售收入如何确定？
+原国税函[2008]828号第三条（已被废止）曾规定自产资产按同类资产同期对外销售价格确定收入。现根据《国家税务总局关于企业所得税有关问题的公告》（国家税务总局公告[2016]80号）第二条的替代规定：应按照被移送资产的公允价值确定销售收入4。
+本案例中，市场零售价10万元即为该批化妆品的公允价值。
+3. 具体调整金额：
+调整项目	金额	说明
+视同销售收入（调增）	+10万元	按公允价值（市场零售价）确认
+视同销售成本（调减）	-8万元	按计税基础（成本）确认
+视同销售净调增	+2万元	计入应纳税所得额
+在年度纳税申报表中，上述调整通过 A105010《视同销售和房地产开发企业特定业务纳税调整明细表》 填报，最终汇总至A105000《纳税调整项目明细表》7。
+二、广告宣传费税前扣除限额调整
+1. 化妆品企业的特殊扣除比例
+《企业所得税法实施条例》第四十四条规定，一般企业发生的广告费和业务宣传费支出，不超过当年销售（营业）收入**15%**的部分准予扣除2。
+但化妆品制造企业适用特殊优惠政策。根据《财政部、税务总局关于广告费和业务宣传费支出税前扣除有关事项的公告》（财政部、税务总局公告[2020]43号）第一条：对化妆品制造或销售企业发生的广告费和业务宣传费支出，不超过当年销售（营业）收入**30%**的部分，准予扣除；超过部分，准予在以后纳税年度结转扣除5。
+该公告有效期至2025年12月31日，因此2025年度汇算清缴完全适用。
+注：新发布的《财政部、税务总局公告[2025]16号》延续了30%的比例，但自2026年1月1日起执行6。
+2. 销售（营业）收入基数的确定
+此处需要特别注意：视同销售收入10万元应当计入"销售（营业）收入"基数，作为计算广告宣传费扣除限额的基础。
+即：广告宣传费扣除限额 = （全年常规销售收入 + 视同销售收入10万元）× 30%
+3. 会计入账金额与扣除限额比较
+项目	金额
+会计入账广告宣传费	8万元（按成本价）
+税前扣除限额	（全年销售营业收入 + 10万视同销售收入）× 30%
+若 8万元 ≤ 扣除限额 → 无需调整，8万元可全额扣除
+若 8万元 &gt; 扣除限额 → 超限部分调增应纳税所得额，超出部分可结转以后年度扣除
+在年度纳税申报表中，通过 A105060《广告费和业务宣传费等跨年度纳税调整明细表》 填报7。
+三、两项调整的综合影响
+调整事项	应纳税所得额影响	备注
+视同销售净调增	+2万元	确定发生
+广告宣传费限额调整	视具体情况而定	需结合全年收入计算
+综合示例（假设该企业全年常规销售收入为X万元）：
+视同销售净调增：+2万元
+广告宣传费扣除限额：（X + 10）× 30%
+若 8万元 ≤（X + 10）× 30%，即 X ≥ 16.67万元，则广告费无需额外调整
+若 X &lt; 16.67万元，则超限部分（8 -（X+10）×30%）需调增
+实务提示
+公允价值的确定：本案以市场零售价10万元作为公允价值。实务中，若企业正常销售渠道为批发而非零售，税务机关可能要求采用企业同类产品的实际对外销售价格（如出厂价/批发价）作为公允价值，而非终端零售价。
+消费税的影响：化妆品属于消费税应税范围，自产自用用于广告宣传还涉及消费税的视同销售处理。消费税可作为税金在企业所得税前扣除（不属于增值税和所得税本身），如涉及需一并考虑。
+申报表填报：2025年度汇算清缴适用《国家税务总局关于优化企业所得税年度纳税申报表的公告》（国家税务总局公告[2025]1号）修订后的申报表7。视同销售调整在A105010填报，广告宣传费调整在A105060填报。
+建议：实务中，建议与主管税务机关确认公允价值的认定口径，以及是否需要同步调整广告费的计税基础（部分地方税务机关认为广告费也应按公允价值10万元确认，而非成本价8万元）。
+</t>
     </r>
     <r>
       <rPr>
@@ -788,8 +2698,47 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> 已过期	财税[2009]69号第一条、国发[2007]39号	过渡期已结束，当前不可适用；且国税函[2010]157号已明确限制
-西部大开发15%税率+定期减免税减半期（7.5%）	</t>
+      <t xml:space="preserve"> 以上分析仅供参考，具体操作请以主管税务机关的口径为准，建议结合企业实际情况咨询专业税务顾问。
+引用文件：
+[1] 中华人民共和国企业所得税法
+[2] 中华人民共和国企业所得税法实施条例
+[3] 国家税务总局关于企业处置资产所得税处理问题的通知（国税函[2008]828号）
+[4] 国家税务总局关于企业所得税有关问题的公告（国家税务总局公告[2016]80号）
+[5] 财政部、税务总局关于广告费和业务宣传费支出税前扣除有关事项的公告（财政部、税务总局公告[2020]43号）
+[6] 财政部、税务总局关于广告费和业务宣传费支出税前扣除有关事项的公告（财政部、税务总局公告[2025]16号）
+[7] 国家税务总局关于优化企业所得税年度纳税申报表的公告（国家税务总局公告[2025]1号）以上分析已完成，所有法规文件均已逐一检索并验证引用链接。如需对某一调整事项作进一步探讨，欢迎继续提问。</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>尝试了三次提问，回答情况不同： 
+第一次：需要纠正税种范围（误认为与消费税相关），修正后，逻辑基本正确，视同销售收入、成本以及广宣费纳税调整正确，但未找到财政部、税务总局公告[2025]16号文中对化妆品广宣费扣除的特别限额规定。
+第二次：税种认定正确，纳税调整正确（不及第一次回答中提及汇算清缴调整表格的精细度），能找到最新广宣费扣除限额文件，且提供计算样本。
+第三次（即贴在左栏的版本）：纳税调整错误，其他项里应额外调减2万广宣费。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">核心结论
+化妆品生产企业将自产化妆品用于广告宣传，2025年企业所得税汇算清缴时需要进行两项纳税调整：
+视同销售调整：调增视同销售收入10万元，调增视同销售成本8万元
+广告费扣除限额调整：需计算广告费是否超过当年销售（营业）收入30%的限额
+详细分析
+一、视同销售收入调整
+第一步：判断是否构成视同销售
+根据《中华人民共和国企业所得税法实施条例》第二十五条规定，企业将货物用于广告等用途的，应当视同销售货物1。
+同时，《国家税务总局关于企业处置资产所得税处理问题的通知》（国税函[2008]828号）第二条明确规定，企业将资产用于市场推广或销售，因资产所有权属已发生改变而不属于内部处置资产，应按规定视同销售确定收入2。
+第二步：确定视同销售收入金额
+根据《国家税务总局关于企业所得税有关问题的公告》（国家税务总局公告[2016]80号）第二条规定，企业发生视同销售情形的，除另有规定外，应按照被移送资产的公允价值确定销售收入3。
+具体调整：
+项目	会计处理	税务处理	纳税调整
+视同销售收入	0	10万元（公允价值/市场零售价）	调增10万元
+视同销售成本	8万元（已计入广告费）	8万元	调增8万元
+净影响	—	—	调增应纳税所得额2万元
+二、广告费税前扣除限额调整
+第一步：确认适用扣除比例
+根据《财政部、税务总局关于广告费和业务宣传费支出税前扣除有关事项的公告》（财政部、税务总局公告[2020]43号）第一条规定，对化妆品制造或销售企业发生的广告费和业务宣传费支出，不超过当年销售（营业）收入**30%**的部分，准予扣除；超过部分，准予在以后纳税年度结转扣除4。
+</t>
     </r>
     <r>
       <rPr>
@@ -808,15 +2757,718 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> 有限可行	税务总局公告2012年第12号第五条	仅限"定期减免税减半期"内，不适用于项目所得减半征收情形；西部大开发政策本身需持续符合条件
-引用列表
-[1] 国家税务总局关于进一步明确企业所得税过渡期优惠政策执行口径问题的通知（国税函[2010]157号）
-[2] 财政部、国家税务总局关于执行企业所得税优惠政策若干问题的通知（财税[2009]69号）
-[3] 国务院关于实施企业所得税过渡优惠政策的通知（国发[2007]39号）
-[4] 国家税务总局关于深入实施西部大开发战略有关企业所得税问题的公告（国家税务总局公告2012年第12号）
-[5] 中华人民共和国企业所得税法（2018修订版）
-[6] 中华人民共和国企业所得税法实施条例（国务院令第512号）</t>
-    </r>
+      <t xml:space="preserve"> 注意：该公告执行期限为2021年1月1日至2025年12月31日，2025年度汇算清缴仍适用30%的扣除比例。
+第二步：计算扣除限额
+广告费税前扣除的关键计算要素：
+项目	说明
+税前扣除限额	当年销售（营业）收入 × 30%
+广告费支出基数	会计入账8万元（成本）
+视同销售收入	10万元（应计入销售（营业）收入）
+重要提示：
+视同销售收入10万元应计入"销售（营业）收入"基数，用于计算广告费扣除限额
+若8万元广告费未超过扣除限额，可全额税前扣除，无需调整
+若超过限额，超限额部分需调增应纳税所得额，并可结转以后年度扣除
+三、汇算清缴填报指引
+在企业所得税年度纳税申报表中，需填报以下表单：
+《视同销售和房地产开发企业特定业务纳税调整明细表》（A105010）
+填报视同销售收入10万元、视同销售成本8万元
+《广告费和业务宣传费等跨年度纳税调整明细表》（A105060）
+填报广告费支出8万元
+计算30%扣除限额，判断是否超限额
+《纳税调整项目明细表》（A105000）
+汇总上述调整金额
+政策依据
+编号	法规文件名	链接
+[1]	中华人民共和国企业所得税法实施条例	查看
+[2]	国家税务总局关于企业处置资产所得税处理问题的通知（国税函[2008]828号）	查看
+[3]	国家税务总局关于企业所得税有关问题的公告（国家税务总局公告[2016]80号）	查看
+[4]	财政部、税务总局关于广告费和业务宣传费支出税前扣除有关事项的公告（财政部、税务总局公告[2020]43号）	查看
+[5]	国家税务总局关于修订企业所得税年度纳税申报表有关问题的公告（国家税务总局公告[2019]41号）	查看
+[6]	国家税务总局关于优化企业所得税年度纳税申报表的公告（国家税务总局公告[2025]1号）	查看
+[7]	财政部、税务总局关于广告费和业务宣传费支出税前扣除有关事项的公告（财政部、税务总局公告[2025]16号）	查看
+实务提示
+视同销售收入需并入销售（营业）收入：10万元视同销售收入不仅影响视同销售调整，还应计入计算广告费扣除限额的销售（营业）收入基数。
+公允价值的确定：本案例中市场零售价10万元即为公允价值。实务中若无明确市场价，可参考同类产品同期对外销售价格。
+广告费结转：若广告费超过30%限额，超限额部分可无限期结转以后年度扣除。
+建议核实：以上分析基于现行法规，实务中建议结合企业具体情况并咨询主管税务机关确认。</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>回答错误。视同销售与视同销售成本的2万差额应调整至广宣费，填入申报表“其他”项并纳入限额测试。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>核心结论
+化妆品生产企业将自产化妆品用于广告宣传，在2025年企业所得税汇算清缴时需要进行视同销售和广告费金额的双重纳税调整。但由于视同销售差额与广告费调增金额相互抵销，最终对应纳税所得额的影响为零。
+分析过程
+第一步：判断是否构成视同销售
+根据《中华人民共和国企业所得税法实施条例》第二十五条规定，企业将货物用于广告等用途的，应当视同销售货物1。
+根据《国家税务总局关于企业处置资产所得税处理问题的通知》（国税函[2008]828号）第二条规定，企业将资产用于市场推广或销售，因资产所有权属已发生改变，应按规定视同销售确定收入2。
+结论：自产化妆品用于广告宣传，属于视同销售情形。
+第二步：确定视同销售价格
+根据《国家税务总局关于企业所得税有关问题的公告》（国家税务总局公告[2016]80号）第二条规定，企业发生视同销售情形的，除另有规定外，应按照被移送资产的公允价值确定销售收入3。
+项目	金额	说明
+视同销售收入	10万元	按公允价值（市场零售价）确定
+视同销售成本	8万元	按资产成本确定
+第三步：纳税调整具体操作
+调整一：视同销售收入和成本的调整
+在《视同销售和房地产开发企业特定业务纳税调整明细表》（A105010）中填报：
+项目	账载金额	税收金额	调增金额
+视同销售收入	0	10万元	10万元
+视同销售成本	0	8万元	8万元
+净影响：视同销售调增应纳税所得额 = 10 - 8 = 2万元
+调整二：广告费金额的调整（调整链条的第二步）
+根据方法论中的"调整事项的完整链条"原则，完成第一步视同销售调整后，必须追问调整产生的差额如何处理。
+对比项	会计处理	税务处理	差异
+广告费入账金额	8万元（按成本）	10万元（按公允价值）	2万元
+原理说明：税务上视同销售确认了10万元收入和8万元成本，意味着企业"卖出了10万元的货，又花了10万元做广告"。因此，税务认可的广告费应为10万元，而非会计入账的8万元。
+在《纳税调整项目明细表》（A105000）相关行次或A105010中，需要同步调减广告费2万元（即调减应纳税所得额2万元），使税务认可的广告费达到10万元。
+调整三：广告费扣除限额的计算
+根据《财政部、税务总局关于广告费和业务宣传费支出税前扣除有关事项的公告》（财政部、税务总局公告[2020]43号），2025年度适用该政策：化妆品制造企业发生的广告费和业务宣传费支出，不超过当年销售（营业）收入30%的部分，准予扣除4。
+在《广告费和业务宣传费跨年度纳税调整明细表》（A105060）中：
+税务认可的广告费支出：10万元
+扣除限额：当年销售（营业）收入 × 30%
+若10万元未超过扣除限额，则可全额扣除
+综合影响汇总
+调整项目	调增金额	调减金额	对应纳税所得额影响
+视同销售收入	10万元	—	+10万元
+视同销售成本	8万元	—	-8万元
+广告费金额调整（差额）	—	2万元	-2万元
+合计	—	—	0
+实务操作提示
+申报表填报：需填报A105010《视同销售和房地产开发企业特定业务纳税调整明细表》和A105060《广告费和业务宣传费跨年度纳税调整明细表》
+注意调整链条完整性：切勿只做视同销售调整而忽略广告费金额的配套调整，否则会导致重复征税
+扣除限额动态计算：视同销售收入10万元应计入当年销售（营业）收入基数，影响广告费扣除限额的计算
+建议核实：实际操作中建议与主管税务机关确认具体的申报填报方式
+政策依据
+[1] 《中华人民共和国企业所得税法实施条例》国务院令第512号
+[2] 《国家税务总局关于企业处置资产所得税处理问题的通知》国税函[2008]828号
+[3] 《国家税务总局关于企业所得税有关问题的公告》国家税务总局公告[2016]80号
+[4] 《财政部、税务总局关于广告费和业务宣传费支出税前扣除有关事项的公告》财政部、税务总局公告[2020]43号
+[5] 《国家税务总局关于优化企业所得税年度纳税申报表的公告》国家税务总局公告[2025]1号
+提示：以上分析基于现行法规，具体操作请以主管税务机关的实际要求为准，建议在汇算清缴前与税务机关确认。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>建议核心结论增加前提“不超过广宣费扣除限额的情况下”，最终应纳税所得额的影响为零。这点在下面分析中有体现，但未反应在结论中。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>关于化妆品生产企业自产货物用于广告宣传的2025年度企业所得税汇算清缴税务处理分析
+针对贵司提出的关于将自产化妆品用于广告宣传在2025年度企业所得税汇算清缴中的税务处理问题，本备忘录基于中国现行有效的企业所得税法律法规进行了全面评估与合规分析。
+1. 核心结论与行动建议
+在假设不考虑增值税影响的前提下，贵司将成本为8万元、市场零售价为10万元的自产化妆品用于广告宣传，在2025年度企业所得税汇算清缴时，需进行两项双向纳税调整，在广告费未超过税前扣除限额的情况下，该事项的净纳税调整额为0。
+具体行动建议如下：
+视同销售调整（调增2万元）： 确认视同销售收入10万元，同时结转视同销售成本8万元，净调增应纳税所得额2万元。
+广告费支出调整（调减2万元）： 税法认可的广告费实际发生额应按公允价值（10万元）确认，相较于会计入账的8万元，需调减应纳税所得额2万元。
+扩大扣除限额基数： 务必将上述10万元视同销售收入计入2025年度广告费和业务宣传费税前扣除限额的计算基数（即销售/营业收入总额）中。
+2. 税务合规分析
+事项一：视同销售的确认与计量
+根据《中华人民共和国企业所得税法实施条例》第二十五条¹及《国家税务总局关于企业处置资产所得税处理问题的通知》（国税函〔2008〕828号）第二条²的规定，企业将资产用于市场推广或销售（如广告宣传），因资产所有权属已发生改变，在企业所得税上不属于内部处置资产，必须视同销售确定收入。
+在计量方面，根据《国家税务总局关于企业所得税有关问题的公告》（国家税务总局公告2016年第80号）第二条³，视同销售应按照被移送资产的公允价值确定销售收入。因此，贵司应按市场零售价确认视同销售收入10万元，并按实际生产成本确认视同销售成本8万元。
+事项二：广告费支出的税前扣除与限额计算
+1. 广告费实际发生额的税法确认
+由于用于广告宣传的资产公允价值为10万元，税法上确认的广告费实际发生额应为10万元。贵司会计核算仅按成本结转了8万元的销售费用（广告费），因此在汇算清缴时，税法允许扣除的金额比会计入账金额多2万元，形成纳税调减事项。
+2. 适用30%的特定行业扣除限额
+根据《财政部 税务总局关于广告费和业务宣传费支出税前扣除有关事项的公告》（财政部 税务总局公告2020年第43号）第一条及第四条</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>⁴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，对化妆品制造或销售企业发生的广告费和业务宣传费支出，不超过当年销售（营业）收入30%的部分，准予扣除。该政策明确执行至2025年12月31日，完全适用于贵司2025年度的汇算清缴。
+3. 视同销售收入增加扣除基数
+根据《国家税务总局关于企业所得税执行中若干税务处理问题的通知》（国税函〔2009〕202号）第一条</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>⁵</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">，企业在计算广告费和业务宣传费扣除限额时，其销售（营业）收入额应包括视同销售（营业）收入额。因此，前述确认的10万元视同销售收入，将合法合规地增加贵司当年广告费的税前扣除基数。
+3. 申报表填报指引
+在进行2025年度企业所得税汇算清缴（填报《中华人民共和国企业所得税年度纳税申报表（A类）》）时，建议按以下路径进行表单填报：
+《A105010 视同销售和房地产开发企业特定业务纳税调整明细表》
+第2行“（一）用于市场推广或销售视同销售收入”：填报 100,000 元。
+第12行“（一）用于市场推广或销售视同销售成本”：填报 80,000 元。
+(此表将自动汇总至主表，产生20,000元的调增效果)
+《A105060 广告费和业务宣传费等跨期扣除项目明细表》
+第1行“本年计算广告费和业务宣传费扣除限额的销售（营业）收入”：应确保包含上述 100,000 元视同销售收入。
+第2行“本年广告费和业务宣传费支出”：填报税收确认金额 100,000 元（假设本年无其他广告费）。
+第4行“本年广告费和业务宣传费支出会计核算金额”：填报 80,000 元。
+第5行“本年广告费和业务宣传费支出纳税调整金额”：填报 -20,000 元（调减）。
+4. 风险提示与合规建议
+增值税视同销售风险： 尽管本咨询假设暂不考虑增值税，但在实务操作中，将自产货物用于广告宣传同样构成增值税视同销售，需按公允价值（10万元）计算销项税额。若未依法计提，将面临税务稽查补税及滞纳金风险。
+证据链留存要求： 税务机关在核查广告费时，通常要求企业提供充分的证据链。建议贵司妥善保存广告发布协议、现场派发照片、签收单据及内部审批文件等证明材料，以防范该笔支出被税务机关重新定性为“非广告性质的赞助支出”（不可税前扣除）或“业务招待费”（面临60%及千分之五的严苛扣除限额）。
+5. 参考法规
+¹ 《中华人民共和国企业所得税法实施条例》，第二十五条
+检索日期：2026-03-30
+第二十五条 企业发生非货币性资产交换，以及将货物、财产、劳务用于捐赠、偿债、赞助、集资、广告、样品、职工福利或者利润分配等用途的，应当视同销售货物、转让财产或者提供劳务，但国务院财政、税务主管部门另有规定的除外。
+² 《国家税务总局关于企业处置资产所得税处理问题的通知》（国税函〔2008〕828号），第二条、第三条
+检索日期：2026-03-30
+二、企业将资产移送他人的下列情形，因资产所有权属已发生改变而不属于内部处置资产，应按规定视同销售确定收入。
+（一）用于市场推广或销售；
+……
+三、企业发生本通知第二条规定情形时，属于企业自制的资产，应按企业同类资产同期对外销售价格确定销售收入；属于外购的资产，可按购入时的价格确定销售收入。
+³ 《国家税务总局关于企业所得税有关问题的公告》（国家税务总局公告2016年第80号），第二条
+检索日期：2026-03-30
+二、企业发生《国家税务总局关于企业处置资产所得税处理问题的通知》（国税函〔2008〕828号）第二条规定情形的，除另有规定外，应按照被移送资产的公允价值确定销售收入。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>⁴</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 《财政部 税务总局关于广告费和业务宣传费支出税前扣除有关事项的公告》（财政部 税务总局公告2020年第43号），第一条、第四条
+检索日期：2026-03-30
+一、对化妆品制造或销售、医药制造和饮料制造（不含酒类制造）企业发生的广告费和业务宣传费支出，不超过当年销售（营业）收入30%的部分，准予扣除；超过部分，准予在以后纳税年度结转扣除。
+……
+四、本通知自2021年1月1日起至2025年12月31日止执行。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>⁵</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 《国家税务总局关于企业所得税执行中若干税务处理问题的通知》（国税函〔2009〕202号），第一条
+检索日期：2026-03-30
+一、关于销售（营业）收入基数的确定问题
+企业在计算业务招待费、广告费和业务宣传费等费用扣除限额时，其销售（营业）收入额应包括《实施条例》第二十五条规定的视同销售（营业）收入额。
+This inquiry requires an advanced level of legal depth, including strategic risk assessment and detailed case law research. To ensure the highest level of accuracy and authoritative citations, we recommend using Legal Research Pro.
+The information and materials provided by this AI-powered research function ("the Service") are generated by an artificial intelligence system and are for informational and research purposes only. The content provided is not intended to be, and should not be construed as, legal or other professional advice on any subject matter. You should not act or refrain from acting based on any information provided by the Service without seeking professional legal counsel, or other professional counsel.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>正确。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>针对化妆品生产企业自产货物用于广告宣传的2025年度企业所得税汇算清缴纳税调整法律备忘录
+A. 执行摘要
+核心发现
+针对贵司（化妆品生产企业）在2025年将成本为8万元、市场零售价为10万元的自产化妆品用于广告宣传的税务处理问题，基于中国现行企业所得税法律法规及国家税务总局的监管指引，核心发现如下：
+视同销售的强制确认：该行为在企业所得税上构成“视同销售”，必须按公允价值（10万元）确认视同销售收入，并按账面成本（8万元）结转视同销售成本，产生2万元的视同销售所得。
+广宣费扣除比例的适用：作为化妆品生产企业，在2025年度依然适用当年销售（营业）收入30%的广告费和业务宣传费（以下简称“广宣费”）税前扣除限额优惠政策。
+扣除基数的合法扩容：确认的10万元视同销售收入必须计入当期销售（营业）收入，从而使企业2025年度的广宣费税前扣除限额增加3万元（10万 × 30%）。
+广宣费实际发生额的对称调增：这是实务中最易错漏的环节。在确认10万元视同销售收入的同时，税法允许将广宣费的实际发生额从会计账载的8万元调增至公允价值10万元，从而完美对冲视同销售产生的2万元“虚增”利润。
+风险评估
+本事项的整体税务风险评级为高。主要风险点在于“单边调整”导致的重复征税。实务中，大量企业财务人员仅在申报表中调增了视同销售收入（10万）和调减了视同销售成本（8万），却遗漏了对广宣费支出的对应调增（2万）。这将导致企业白白为2万元的内部未实现利润缴纳25%（即5,000元）的企业所得税。此外，若未将10万元视同销售收入计入广宣费扣除基数，将导致扣除限额计算错误，引发税务稽查风险。
+核心建议
+建议企业在2025年度企业所得税汇算清缴时，严格执行“三表联动”的纳税调整策略：首先在《视同销售和房地产开发企业特定业务纳税调整明细表》（A105010）中确认收入与成本；其次在《纳税调整项目明细表》（A105000）第30行填报2万元的费用差异调减；最后在《广告费和业务宣传费等跨年度纳税调整明细表》（A105060）中准确归集基数与实际发生额，确保税务处理的完整性与合规性。
+B. 核心问题分析与策略路径
+问题定义与商业背景
+在化妆品行业的商业推广中，将自产产品作为样品派发或用于广告宣传是极为常见的营销手段。本案中，企业将成本8万元、公允价值10万元的自产化妆品用于广告宣传。
+在财务会计处理上，根据企业会计准则，企业通常不确认营业收入，而是直接按产品成本（8万元）借记“销售费用——广告费”，贷记“库存商品”。
+然而，在企业所得税法视角下，该资产的所有权已跨越企业法人实体转移至外部，触发了“视同销售”条款。这就产生了核心的税会差异冲突：会计上无收入、费用为8万；税法上要求有收入（10万）、有成本（8万），且对费用的认定金额存在争议。企业的商业诉求是在合法合规的前提下，准确进行纳税调整，避免因税会差异导致多缴税款或面临税务行政处罚。
+策略路径比较
+针对该事项的纳税调整，实务中存在以下几种处理路径：
+策略路径	可行性	法律依据	核心法律与实务风险
+路径 A：仅按会计口径申报（不作任何纳税调整）	极低	无合法依据	严重违反《企业所得税法实施条例》第25条，构成偷漏税，面临补税、滞纳金及罚款风险。
+路径 B：单边调整（仅确认视同销售收入10万与成本8万，广宣费按8万扣除）	低	《企业所得税法实施条例》第25条 [22]	产生2万元应纳税所得额，导致企业为未实现的内部利润缴纳真金白银的所得税，违背税收中性原则。
+路径 C：双向对称调整（确认视同销售收支，同时将广宣费计税基础调增至10万）（推荐）	极高	《国家税务总局关于修订企业所得税年度纳税申报表有关问题的公告》 [24]	需严格保留公允价值（10万元）的定价证据，防范税务机关对公允价值合理性的质疑。
+策略路径深度分析：
+路径 A（不作调整）：完全忽略了税法的强制性规定。税务稽查系统通过大数据比对（如增值税销项税额与企业所得税收入的差异）极易发现此项违规，属于绝对的合规红线。
+路径 B（单边调整）：这是过去部分基层税务机关和保守财务人员常用的做法。其逻辑是严格恪守“实际发生”原则，认为企业实际流出的经济利益仅为8万元成本。但这种做法割裂了视同销售的法理本质，导致企业税负畸高，在现行国家税务总局的申报表规则下已被纠正。
+路径 C（双向对称调整）：这是目前唯一合法且最优的策略。其底层逻辑是“分解交易”原则——即税法拟制企业先以10万元将化妆品卖出（确认收入10万、成本8万），随后立刻用取得的10万元现金购买了广告服务（确认广宣费10万）。通过在申报表中进行双向调整，既满足了税法对视同销售的监管要求，又保护了企业的合法税收权益。
+C. 适用法律框架
+本节汇编了适用于本案的核心企业所得税法律法规及官方填报指引。所有引用的法律条文均来源于中国大陆现行有效的官方权威信源（TIER_1）。
+企业所得税基本法规
+官方来源: 《中华人民共和国企业所得税法实施条例》 [22]
+发布机构: 中华人民共和国国务院
+条款: 第二十五条
+原文: "企业发生非货币性资产交换，以及将货物、财产、劳务用于捐赠、偿债、赞助、集资、广告、样品、职工福利或者利润分配等用途的，应当视同销售货物、转让财产或者提供劳务，但国务院财政、税务主管部门另有规定的除外。"
+适用性: 构成本案的根本法律依据，明确界定了将自产货物用于“广告”用途必须作为视同销售处理，确立了纳税调整的法定前提。
+特定行业广宣费扣除政策
+官方来源: 《财政部 税务总局关于广告费和业务宣传费支出税前扣除有关事项的公告》 [7]
+发布机构: 中华人民共和国财政部、国家税务总局
+条款: 第一条及第四条
+原文: "一、对化妆品制造或销售、医药制造和饮料制造（不含酒类制造）企业发生的广告费和业务宣传费支出，不超过当年销售（营业）收入30%的部分，准予扣除；超过部分，准予在以后纳税年度结转扣除。……四、本通知自2021年1月1日起至2025年12月31日止执行。"
+适用性: 确立了贵司作为“化妆品制造企业”在2025年度适用的广宣费税前扣除限额比例为30%，远高于一般企业的15%。
+纳税申报表填报规则（视同销售）
+官方来源: 《中华人民共和国企业所得税年度纳税申报表（A类）》填报说明 [4]
+发布机构: 国家税务总局
+条款: A105010表第11行填报说明
+原文: "第11行“二、视同销售（营业）成本”：填报会计处理不确认销售收入，税收规定确认为应税收入的同时，确认的视同销售成本金额。本行为第12至20行小计数。第1列“税收金额”填报予以税前扣除的视同销售成本金额；将第1列税收金额以负数形式填报第2列“纳税调整金额”。"
+适用性: 为本案中8万元视同销售成本的合法扣除与申报表落位提供了直接的操作依据。
+D. 案例法与执法实践分析
+在中国大陆的成文法体系下，虽然没有严格意义上的判例法，但各级税务机关的官方答疑、执法口径及实务稽查案例对企业的税务合规具有高度的指导意义。针对“视同销售与视同支出”的争议，执法实践呈现出明确的演变趋势。
+执法口径：确立“分解交易”原则
+在早期的税务稽查中，部分地方税务局曾拒绝企业按公允价值确认对应的“视同支出”，导致企业重复缴税。然而，近年来的官方执法口径已全面转向支持“分解交易”原则。
+根据北京市税务局发布的官方指引，税务机关在处理视同销售时，明确采用了分解交易的逻辑 [26]。北京市税务局在相关指引中指出，当企业发生视同销售情形时，在税务处理上应分解为两个独立的行为：一是按照产品的公允价值确认收入，并结转对应成本；二是按照该公允价值确认对应的费用支出（如职工福利费、广告费等） [26]。这一官方表态为企业主张将广宣费实际发生额从账面成本（8万）调增至公允价值（10万）提供了坚实的执法实践支撑。
+稽查重点：市场推广行为的严格定性
+尽管税务机关允许确认视同支出，但对“视同销售”本身的定性依然极为严格。深圳市税务局在2025年的官方热点问答中重申了对市场推广行为的执法态度，明确指出企业将资产移送他人用于市场推广或销售的，因资产所有权属已发生改变，必须按规定视同销售确定收入 [14]。
+这表明，在税务稽查实践中，税务机关的首要关注点是企业是否隐瞒了视同销售收入。如果企业以“用于内部广告宣传”为由拒绝确认10万元的视同销售收入，将直接触发偷漏税的稽查红线。只有在依法确认收入的前提下，企业才有资格主张对应费用的调增。
+E. 详细法律分析
+针对贵司2025年将自产化妆品用于广告宣传的事项，以下将运用IRAC方法论，对四个核心税务问题进行深度剖析。
+核心问题一：视同销售行为的界定与计价标准
+A. 适用法律标准
+根据《中华人民共和国企业所得税法实施条例》第二十五条规定，企业将货物用于广告用途的，应当视同销售货物 [22]。此外，国家税务总局《关于企业所得税有关问题的公告》（2016年第80号）第二条明确规定，企业发生资产移送情形的，除另有规定外，应按照被移送资产的公允价值确定销售收入 [2]。
+B. 事实分析与应用
+本案中，贵司将自产的化妆品用于广告宣传（如向潜在客户派发、在活动中赠送等），该化妆品的法定所有权已经从贵司转移至接受方。这种跨越法人实体的资产流出，完全符合税法关于“资产所有权属改变”的界定。
+在计价方面，税法已于2016年废止了原有的“同类资产同期对外销售价格”标准，全面适用“公允价值”原则 [2]。因此，该批化妆品的市场零售价10万元即为其公允价值。
+C. 法律后果
+贵司在2025年度企业所得税汇算清缴时，必须单方面确认视同销售收入10万元，同时允许结转其计税基础（即账面成本）8万元作为视同销售成本。此步骤将初步产生2万元的视同销售所得。
+核心问题二：2025年度化妆品企业广宣费扣除限额的适用
+A. 适用法律标准
+根据《财政部 税务总局关于广告费和业务宣传费支出税前扣除有关事项的公告》（2020年第43号）第一条及第四条，化妆品制造企业发生的广告费和业务宣传费支出，不超过当年销售（营业）收入30%的部分，准予扣除；该政策执行至2025年12月31日 [7]。
+B. 事实分析与应用
+贵司的主营业务为化妆品生产，属于该公告明确列举的特定受惠行业。由于本案发生于2025年，完全处于该政策的法定有效期限内。因此，贵司在计算当年度广宣费扣除上限时，无需适用一般企业15%的比例，而应适用30%的高比例限额。
+C. 补充说明与政策延续
+值得注意的是，根据最新发布的《财政部 税务总局关于广告费和业务宣传费支出税前扣除有关事项的公告》（2025年第16号），该30%的优惠政策已被无缝延续至2027年12月31日 [6]。这为贵司未来的营销预算与税务筹划提供了长期的政策确定性。
+核心问题三：视同销售收入对广宣费扣除基数的扩容效应
+A. 适用法律标准
+根据《国家税务总局关于企业所得税执行中若干税务处理问题的通知》（国税函〔2009〕202号）第一条规定，企业在计算业务招待费、广告费和业务宣传费等费用扣除限额时，其销售（营业）收入额应包括《实施条例》第二十五条规定的视同销售（营业）收入额 [23]。
+B. 事实分析与应用
+广宣费的税前扣除限额并非一个绝对数值，而是基于“销售（营业）收入”动态计算的。本案中，贵司因广告宣传行为确认了10万元的视同销售收入。根据上述规定，这10万元不能孤立存在，而必须加总至贵司2025年度的主营业务收入和其他业务收入中，共同构成广宣费的计算基数。
+C. 法律后果
+这10万元的基数扩容，将直接导致贵司2025年度的广宣费税前扣除限额增加3万元（10万元 × 30%）。这意味着，如果贵司当年的实际广宣费支出总额较大，这额外增加的3万元额度将允许贵司在税前多扣除3万元的费用，从而实现实质性的税负降低。
+核心问题四：广宣费实际发生额的对称调增（消除虚增利润）
+A. 适用法律标准
+根据《国家税务总局关于修订企业所得税年度纳税申报表有关问题的公告》（2019年第41号）附件填报说明，关于《纳税调整项目明细表》（A105000）第30行“（十七）其他”的规定：“企业将货物、资产、劳务用于捐赠、广告等用途时，进行视同销售纳税调整后，对应支出的会计处理与税收规定有差异需纳税调整的金额填报在本行。” [24]
+B. 事实分析与应用
+这是本案税务处理中最核心的争议解决点。贵司在会计处理上，仅按成本价确认了8万元的广告费用。但在税法“双重虚拟交易”的逻辑下，既然税法强制拟制贵司以10万元公允价值卖出了商品，就必须同时拟制贵司用这10万元支付了广告费。
+2019年第41号公告的填报说明正式在实务操作层面支持了这一对称逻辑 [24]。税法认定的广宣费实际发生额应为10万元，与会计账载的8万元之间存在2万元的差异。
+C. 法律后果
+贵司有权在A105000表第30行填报这2万元的差异作为“纳税调减”。这一调减动作将完美抵消核心问题一中产生的2万元视同销售所得，确保贵司不会因为将自产货物用于广告而产生额外的企业所得税负担（前提是调整后的广宣费总额未超过30%的限额）。
+F. 缺失事实与信息缺口
+为提供最终的、精确到个位数的税务计算结果，本备忘录的分析基于现有事实，但仍需贵司补充以下关键信息：
+1. 2025年度整体营收与费用数据
+年度总销售（营业）收入：需明确贵司2025年度的主营业务收入和其他业务收入总额，以便准确计算广宣费的整体扣除限额。
+年度广宣费实际发生总额：除本案涉及的8万元（会计口径）外，贵司在2025年实际发生的其他广告费和业务宣传费总额是多少？这将决定调增后的广宣费是否会突破30%的上限。
+2. 历史结转数据
+以前年度结转的广宣费：贵司在2024年及以前年度，是否存在因超标而结转至本年度扣除的广宣费余额？若有，本案中扩容的3万元扣除限额可用于吸收这些历史结转费用。
+3. 增值税处理细节
+虽然本次咨询假设不考虑增值税影响，但在实际操作中，将自产货物用于广告宣传同样触发增值税视同销售，需按10万元计算销项税额（通常为1.3万元）。这笔增值税金在会计上通常也计入“销售费用”，并构成合法的广宣费税前扣除基数。贵司需确认该笔增值税的实际账务处理路径。
+G. 实务影响与合规指南
+为确保上述法律分析在2025年度企业所得税汇算清缴中准确落地，防范税务稽查风险，贵司财务部门需严格按照以下指引进行申报表填报：
+步骤一：填报视同销售明细表（A105010）
+确认收入：在A105010《视同销售和房地产开发企业特定业务纳税调整明细表》第2行“（一）非货币性资产交换视同销售收入”或第7行“用于市场推广或推销视同销售收入”的第1列“税收金额”和第2列“纳税调整金额”中，填报公允价值 100,000元（作纳税调增）。
+结转成本：在该表第12行“（一）非货币性资产交换视同销售成本”或第17行“用于市场推广或推销视同销售成本”的第1列“税收金额”填报账面成本 80,000元，并在第2列“纳税调整金额”以负数形式填报 -80,000元（作纳税调减） [4]。
+步骤二：填报费用差异调整（A105000）
+消除虚增利润：进入A105000《纳税调整项目明细表》，在第30行“（十七）其他”的第4列“调减金额”中，填报公允价值与账面成本的差额 20,000元 [24]。此举至关重要，是防止企业为未实现利润交税的核心步骤。
+步骤三：填报广宣费跨期调整表（A105060）
+扩大计算基数：在A105060《广告费和业务宣传费等跨年度纳税调整明细表》第4行“三、本年计算扣除限额的基数”中，必须确保填报的金额包含了步骤一中确认的 100,000元 视同销售收入。
+归集实际发生额：在该表第1行“一、本年支出”中，填报包含本案8万元在内的所有会计账载广宣费。由于步骤二已在主表作了费用调减，此处需注意电子税务局系统的自动映射逻辑，确保税法认定的广宣费总额包含了调增的2万元。
+H. 战略建议
+基于上述深度法律与税务分析，为优化贵司的税务管理并降低合规风险，提出以下战略建议：
+短期合规建议（针对2025年汇算清缴）
+建立公允价值证据链：由于税法强制要求按公允价值（10万元）确认视同销售收入及对应的广宣费支出，贵司必须妥善保留该批化妆品在2025年同期的市场公开报价单、对外销售发票或第三方评估报告。若税务机关在稽查中认为10万元的公允价值偏高，不仅会调减视同销售收入，更会同步压缩广宣费的调增额度。
+执行年底限额压力测试：在2025年底前，财务部门应结合本案产生的视同销售数据，对全年的广宣费总额进行压力测试。若测算发现调增后的广宣费总额将超过当年销售收入的30%，超额部分将无法在当年扣除，需结转以后年度。此时，企业应考虑适当递延其他非紧急的广告投放至2026年。
+长期税务筹划建议
+完善内部领用审批与账务规范：建议贵司修订内部资产领用制度，在领料单上明确标注“用于广告宣传/市场推广”。在会计核算时，不仅要结转成本，还应同步计提增值税销项税额，确保增值税与企业所得税在“视同销售”定性上的逻辑一致性，阻断税务稽查的疑点。
+利用关联企业分摊机制：根据2020年第43号公告及2025年第16号公告，签订了广宣费分摊协议的关联企业，可以将未超限额的广宣费归集至另一方扣除 [7]。若贵司集团内存在专门的销售公司且其广宣费严重超标，而贵司（制造企业）的30%额度有结余，可通过签订分摊协议，将销售公司的超标费用转移至贵司扣除，实现集团整体税负的最优化。
+I. 结论
+综上所述，贵司在2025年将成本8万元、市场价10万元的自产化妆品用于广告宣传，在企业所得税汇算清缴时必须进行双向的纳税调整。首先，必须按公允价值确认10万元的视同销售收入，并结转8万元的视同销售成本；其次，这10万元的视同销售收入将合法增加贵司广宣费的扣除基数；最关键的是，贵司有权将广宣费的实际发生额从账面成本8万元调增至公允价值10万元。通过在纳税申报表中准确填报上述差异，贵司能够在完全合法合规的前提下，消除视同销售带来的虚增利润，并最大化利用化妆品企业30%的广宣费税前扣除政策红利。
+The information and materials provided by this AI-powered research function (“the Service”) are generated by an artificial intelligence system and are for informational and research purposes only. The content provided is not intended to be, and should not be construed as, legal or other professional advice on any subject matter. You should not act or refrain from acting based on any information provided by the Service without seeking professional legal counsel, or other professional counsel.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>正确。建议精简，策略路线部分不太实用。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>一、上位法依据
+本问题涉及的上位法为：
+《中华人民共和国企业所得税法》
+《中华人民共和国企业所得税法实施条例》
+二、事项分析
+化妆品生产企业将自产化妆品用于广告宣传，该事项在2025年企业所得税汇算清缴时涉及两项纳税调整：
+调整一：视同销售纳税调增
+法规依据：
+《企业所得税法实施条例》第二十五条规定：企业将货物用于广告、样品等用途的，应当视同销售货物2。
+《国家税务总局关于企业处置资产所得税处理问题的通知》（国税函〔2008〕828号）第二条明确：企业将资产用于市场推广或销售，因资产所有权属已发生改变，应按规定视同销售确定收入1。
+关于视同销售收入的确定，原国税函〔2008〕828号第三条已被废止，现按《国家税务总局关于企业所得税有关问题的公告》（国家税务总局公告2016年第80号）第二条规定执行：企业发生视同销售情形的，除另有规定外，应按照被移送资产的公允价值确定销售收入3。
+具体调整：
+项目	金额
+视同销售收入（按公允价值/市场零售价）	+100,000元
+视同销售成本（按实际成本）	+80,000元
+净调增应纳税所得额	+20,000元
+填报表：A105010《视同销售和房地产开发企业特定业务纳税调整明细表》
+调整二：广告宣传费的金额调整与限额扣除
+（1）广告费金额调整
+会计处理按成本8万元入账广告费用。但按照视同销售的逻辑，企业"以公允价值10万元的货物换取了广告宣传服务"，因此：
+会计入账广告费：80,000元（按成本）
+税法口径广告费：100,000元（按公允价值）
+需调增广告费扣除金额：+20,000元（调减应纳税所得额）
+此项调整与调整一的视同销售净调增20,000元正好对冲，这是视同销售中收入端和扣除端联动的结果。
+（2）广告费限额扣除测试
+法规依据：
+《企业所得税法实施条例》第四十四条规定：企业发生的符合条件的广告费和业务宣传费支出，不超过当年销售（营业）收入15% 的部分，准予扣除；超过部分，准予在以后纳税年度结转扣除2。
+但《财政部、税务总局关于广告费和业务宣传费支出税前扣除有关事项的公告》（财政部、税务总局公告2020年第43号）第一条对化妆品制造企业给出了优惠比例：
+对化妆品制造或销售、医药制造和饮料制造（不含酒类制造）企业发生的广告费和业务宣传费支出，不超过当年销售（营业）收入30% 的部分，准予扣除；超过部分，准予在以后纳税年度结转扣除。4
+该公告第四条规定执行至2025年12月31日，因此2025年度汇算清缴完全适用4。
+限额计算公式：
+广告费扣除限额 = 当年销售（营业）收入 × 30%
+其中，"当年销售（营业）收入"基数应包含视同销售收入100,000元（即视同销售收入应并入营业收入基数）。
+填报表：A105060《广告费和业务宣传费等跨年度纳税调整明细表》
+三、调整汇总
+序号	调整事项	调整方向	金额
+1	视同销售收入	调增收入	+100,000元
+2	视同销售成本	调增扣除	+80,000元
+3	广告费金额调整（成本→公允价值）	调增扣除	+20,000元
+4	广告费限额测试	视具体情况	以30%限额为准
+综合来看：
+调整1-3的净效果：视同销售净调增20,000元与广告费金额调增20,000元互相抵消，对所得额的净影响为零。
+调整4是关键：需将税法口径广告费总额（含本次100,000元及其他广告宣传费）与**当年销售（营业）收入×30%**进行比较。若超过限额，超出部分需纳税调增（可结转以后年度扣除）；若未超过，则无需额外调整。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>回答和分析都正确。但广宣费调增金额20,000申报表填写，未告知填列何处，可进一步优化。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025年5月，母子公司吸收合并，导致子公司持有的股票非交易过户给母公司。吸收合并没有支付对价，会计上是按账面净值做的账。该股票非交易过户是否需要缴纳增值税？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1）注意2026.1.1后开始实施新《增值税法》，该日期前后的交易税收规定不同2）查询2026.1.1前，股票转让是否缴纳增值税--&gt;落入金融商品买卖，需要缴纳增值税
+3）理解母子吸收合并属于重组，查询到2026.1.1前，重组不征增值税的特殊规定--&gt;发现该特殊规定没有涵盖股票（金融商品）这个品类，所以无法适用该规定
+4）由于用户提到交易不支付对价、会计按账面净值处理，查询2026.1.1前是否存在无偿转让股票的特殊规定--&gt;可能可以适用无偿转让股票的规定，实际增值税税负为0，但需要确认是否真的“无偿”
+</t>
+  </si>
+  <si>
+    <t>结论：在2025年5月的法律框架下，该股票非交易过户属于增值税应税行为（金融商品转让），但由于没有支付对价，适用无偿转让股票的特殊计税规则，纳税人无偿转让股票时，转出方以该股票的买入价为卖出价，实际应缴纳的增值税为0元。
+具体分析：
+根据2016年36号文，股票交易按照金融商品转让缴纳增值税。
+首先分析2025年5月期间，吸收合并导致的股票非交易过户是否适用“资产重组不征收增值税”？（已核实：不适用）
+资产重组不征税政策的适用性分析（基于2025年5月生效法规）
+根据《财政部 国家税务总局关于全面推开营业税改征增值税试点的通知》（财税〔2016〕36号）附件2的规定，在资产重组过程中，将全部或者部分实物资产以及与其相关联的债权、负债和劳动力一并转让的，其中涉及的“货物、不动产、土地使用权”转让行为，不征收增值税。
+分析：在2025年5月的时点，上述不征税范围采取的是严格列举方式，仅限于货物、不动产和土地使用权，并未包含“金融商品”（如股票）。因此，在当时的税务实践中，吸收合并导致的股票过户无法直接适用资产重组不征收增值税的豁免条款，而应被界定为“金融商品转让”的应税行为。
+其次在无支付对价的前提下，该股票过户如何确定增值税计税销售额？（已核实：适用无偿转让规则，销售额为0）
+在吸收合并过程中“没有支付对价，会计上是按账面净值做的账”，该股票非交易过户在税务处理上构成“无偿转让股票”。
+根据《财政部 税务总局关于明确无偿转让股票等增值税政策的公告》（财政部 税务总局公告2020年第40号）第一条的规定，纳税人无偿转让股票时，转出方以该股票的买入价为卖出价。
+分析：
+转出方（子公司）：需以该股票的原买入价作为本次过户的卖出价。根据金融商品转让“销售额 = 卖出价 - 买入价”的计算公式，本次转让的销售额为0（买入价 - 买入价 = 0），因此无需实际缴纳增值税。
+转入方（母公司）：母公司取得该股票的买入价，依法结转为子公司原先的买入价。
+ [参考依据]
+¹ 《财政部 国家税务总局关于全面推开营业税改征增值税试点的通知》（财税〔2016〕36号）附件2《营业税改征增值税试点有关事项的规定》第一条第（二）项
+在资产重组过程中，通过合并、分立、出售、置换等方式，将全部或者部分实物资产以及与其相关联的债权、负债和劳动力一并转让给其他单位和个人，其中涉及的货物、不动产、土地使用权转让行为。
+² 《财政部 税务总局关于明确无偿转让股票等增值税政策的公告》（财政部 税务总局公告2020年第40号）第一条
+一、纳税人无偿转让股票时，转出方以该股票的买入价为卖出价，按照“金融商品转让”计算缴纳增值税；在转入方将上述股票再转让时，以原转出方的卖出价为买入价，按照“金融商品转让”计算缴纳增值税。
+³ 《财政部 税务总局关于增值税进项税额抵扣等有关事项的公告》（财政部 税务总局公告2026年第13号）第二条第（一）项 （注：2026年1月1日起施行，作参考印证）
+（一）纳税人通过合并、分立、出售、置换等方式实施资产重组，同时符合下列条件的，不属于增值税应税交易和增值税法实施条例第二十二条规定的不得抵扣非应税交易，涉及的货物、金融商品、无形资产、不动产（以下统称资产）转让，不征收增值税，对应的进项税额可以按规定从销项税额中抵扣：</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.[优先行动事项]
+结论先行：在2025年5月的法律框架下，该股票非交易过户属于增值税应税行为（金融商品转让），但由于没有支付对价，适用无偿转让股票的特殊计税规则，实际应缴纳的增值税为0元。
+税务申报合规：虽然应纳税额为0，但转出方（子公司）仍需按照“金融商品转让”进行增值税纳税申报，不可直接按“不征税项目”处理。
+计税基础递延：母公司（转入方）未来再次对外转让该股票时，必须以子公司（原转出方）的原始买入价作为扣除基础计算缴纳增值税，需做好税务台账的交接与留存。
+2. [法律问题拆解]
+本案涉及以下原子化法律问题：
+司法管辖区：中国
+法律领域：税法（增值税）
+适用法律类别：税收规范性文件（财政部、国家税务总局公告）
+核心法律问题：
+2025年5月期间，吸收合并导致的股票非交易过户是否适用“资产重组不征收增值税”的豁免条款？（已核实：不适用）
+在无支付对价的前提下，该股票过户如何确定增值税计税销售额？（已核实：适用无偿转让规则，销售额为0）
+3. [法律分析]
+3.1 资产重组不征税政策的适用性分析（基于2025年5月生效法规）
+根据《财政部 国家税务总局关于全面推开营业税改征增值税试点的通知》（财税〔2016〕36号）附件2的规定，在资产重组过程中，将全部或者部分实物资产以及与其相关联的债权、负债和劳动力一并转让的，其中涉及的“货物、不动产、土地使用权”转让行为，不征收增值税。
+分析：在2025年5月的时点，上述不征税范围采取的是严格列举方式，仅限于货物、不动产和土地使用权，并未包含“金融商品”（如股票）。因此，在当时的税务实践中，吸收合并导致的股票过户无法直接适用资产重组不征收增值税的豁免条款，而应被界定为“金融商品转让”的应税行为。
+3.2 无偿转让股票的特殊计税规则
+鉴于贵司在吸收合并过程中“没有支付对价，会计上是按账面净值做的账”，该股票非交易过户在税务处理上构成“无偿转让股票”。
+根据《财政部 税务总局关于明确无偿转让股票等增值税政策的公告》（财政部 税务总局公告2020年第40号）第一条的规定，纳税人无偿转让股票时，转出方以该股票的买入价为卖出价。
+分析：
+转出方（子公司）：需以该股票的原买入价作为本次过户的卖出价。根据金融商品转让“销售额 = 卖出价 - 买入价”的计算公式，本次转让的销售额为0（买入价 - 买入价 = 0），因此无需实际缴纳增值税。
+转入方（母公司）：母公司取得该股票的买入价，依法结转为子公司原先的买入价。
+3.3 商业洞察与政策演进（2026年新规印证）
+作为商业延伸提示，针对“资产重组中金融商品转让是否征税”的长期实务争议，监管部门已出台新规予以彻底解决。自2026年1月1日起施行的《财政部 税务总局关于增值税进项税额抵扣等有关事项的公告》（财政部 税务总局公告2026年第13号）明确将“金融商品”纳入了资产重组不征收增值税的范围。
+虽然贵司的交易发生于2025年5月，无法溯及适用2026年的13号公告，但该新规的出台充分印证了国家税务总局对于“企业重组过程中的资产平移不应实质性增加企业增值税负担”的政策导向。结合2020年第40号公告，贵司在2025年5月的交易实现“零税负”过户是完全符合税法深层逻辑与合规要求的。
+4. [合规与风险提示]
+证据链留存：建议妥善保留吸收合并协议、股东会/董事会决议、资产交割单以及证明“无对价支付”和“按账面净值结转”的会计凭证，以备税务机关核查其“无偿转让”的商业实质。
+发票开具限制：金融商品转让不得开具增值税专用发票。由于本案销售额为0，通常无需开具发票，但需在增值税申报表附表（金融商品转让）中如实填报买入价与卖出价。
+5. [参考依据]
+¹ 《财政部 国家税务总局关于全面推开营业税改征增值税试点的通知》（财税〔2016〕36号）附件2《营业税改征增值税试点有关事项的规定》第一条第（二）项
+检索日期：2026-03-30
+在资产重组过程中，通过合并、分立、出售、置换等方式，将全部或者部分实物资产以及与其相关联的债权、负债和劳动力一并转让给其他单位和个人，其中涉及的货物、不动产、土地使用权转让行为。
+² 《财政部 税务总局关于明确无偿转让股票等增值税政策的公告》（财政部 税务总局公告2020年第40号）第一条
+检索日期：2026-03-30
+一、纳税人无偿转让股票时，转出方以该股票的买入价为卖出价，按照“金融商品转让”计算缴纳增值税；在转入方将上述股票再转让时，以原转出方的卖出价为买入价，按照“金融商品转让”计算缴纳增值税。
+³ 《财政部 税务总局关于增值税进项税额抵扣等有关事项的公告》（财政部 税务总局公告2026年第13号）第二条第（一）项 （注：2026年1月1日起施行，作参考印证）
+检索日期：2026-03-30
+（一）纳税人通过合并、分立、出售、置换等方式实施资产重组，同时符合下列条件的，不属于增值税应税交易和增值税法实施条例第二十二条规定的不得抵扣非应税交易，涉及的货物、金融商品、无形资产、不动产（以下统称资产）转让，不征收增值税，对应的进项税额可以按规定从销项税额中抵扣：</t>
+  </si>
+  <si>
+    <t>正确，还答出了税法演进，如果交易发生在2026年会怎么样。很完整</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>法律研究备忘录：吸收合并下股票非交易过户的增值税处理
+A. 执行摘要
+核心发现
+针对2025年5月母子公司吸收合并导致的股票非交易过户（无对价、按账面净值结转）是否需要缴纳增值税的问题，核心结论取决于所转让股票的性质以及税务机关对历史交易的执法口径：
+股票性质决定根本定性：若该股票为“非上市公司股权”，则根本不属于增值税征收范围，无需缴纳增值税 [18]。若该股票为“上市公司股票”（含限售股），则在税法上构成“金融商品转让” [18]。
+2025年历史交易的税务高风险：由于该吸收合并发生在2025年5月，适用当时的《关于全面推开营业税改征增值税试点的通知》（财税〔2016〕36号）[18]及《国家税务总局公告2011年第13号》[19]。上述历史规定仅明确了“货物、不动产、土地使用权”在资产重组中不征收增值税，未明确豁免“金融商品”。因此，该笔过户面临被税务机关认定为应税交易的高风险。
+“无对价”与“账面净值”的抗辩局限性：在增值税体系下，“无对价”或“按账面净值划转”并不天然构成免税或平价结转的正当理由。若被认定为应税交易，税务机关有权按过户日的公允价值（股票市值）核定销售额并征收增值税 [13]。
+2026年新规的抗辩空间：自2026年1月1日起施行的《财政部 税务总局公告2026年第13号》已明确将“金融商品”纳入资产重组不征税范围 [2]。虽然该新规原则上不溯及2025年的交易，但为企业向税务机关主张“税收中性”的立法本意提供了强有力的谈判依据 [8]。
+风险评估
+税务核定风险（高）：若标的为上市公司股票，基层税务机关极可能依据2025年有效的法规，按股票公允价值核定征收6%的增值税 [8][20]。
+过户程序受阻风险（中）：中国证券登记结算有限责任公司（CSDC）办理非交易过户需审查法人注销证明 [17]。若因子公司未结清增值税导致无法完成税务注销，将直接阻断股票过户程序。
+核心建议
+首要行动是确认标的股票是否为上市公司股票。若是，强烈建议在进行税务注销清算前，利用2026年第13号公告 [2] 的立法精神，与主管税务机关进行专项沟通，争取适用“资产重组不征收增值税”的实质性豁免待遇，避免按公允价值缴纳巨额增值税。
+B. 核心问题分析与策略路径
+问题定义与商业背景
+客户在2025年5月实施了母子公司吸收合并，子公司持有的股票随之非交易过户至母公司。交易特征为“无对价支付”且“按账面净值结转”。
+核心法律冲突在于：
+税法与会计的错位：会计处理和企业所得税（特殊性税务处理）允许同一控制下按账面净值平移，但2025年时期的增值税法对此缺乏明确的平价结转或豁免规定 [8]。
+形式与实质的冲突：形式上，股票所有权发生了转移；实质上，这是企业主体资格消灭导致的资产包概括承受。税务机关是否认可其“重组实质”是决定是否征税的关键 [20]。
+策略路径比较
+策略路径	可行性评估	法律依据	核心法律与实务风险
+路径 A：主张非上市公司股权不征税	极高（若事实相符）	《财税〔2016〕36号》附件1 [18]	仅适用于非上市股权。若为上市公司股票则此路不通。
+路径 B：主张适用资产重组不征税（推荐）	中/高（需税务沟通）	《国家税务总局公告2011年第13号》[19]及《2026年第13号公告》立法精神 [2]	2025年法规未明文包含金融商品，基层税务局可能坚持字面解释强行征税。
+路径 C：主张无偿转让按买入价结转	低	《财税〔2016〕36号》[18]及相关无偿划转规定	吸收合并通常被税务机关视为“有偿”（以注销股权为对价），难以适用纯粹的无偿转让豁免。
+路径 D：接受视同销售但做大买入价	中（备选方案）	《财税〔2016〕36号》差额计税规则 [18]	需缴纳增值税，但可通过合法确认最高历史成本来压缩税基，仍会产生现金流负担。
+策略路径分析：
+路径 A 是最安全的路径，但受限于客观事实。
+路径 B（推荐） 是针对上市公司股票的最优选。虽然交易发生在2025年，但企业应整理完整的“资产、债权、负债、员工一并转让”的证据链，结合2026年新规 [2] 确立的“金融商品免税”政策精神，向税务机关主张实质重于形式，争取不征税批复。
+路径 C 在实务中极易被税务机关驳回，因为吸收合并本质上是母公司以其持有的子公司股权（或发行新股）作为对价换取子公司资产，不符合税法意义上的“无偿”。
+C. 适用法律法规
+本节汇编了适用于本案的中国大陆现行有效及交易发生时（2025年）有效的核心税收法律法规。
+增值税基本定性与计税规则
+官方来源: 《关于全面推开营业税改征增值税试点的通知》（财税〔2016〕36号） [18]
+发布机构: 财政部、国家税务总局
+条款: 附件1《营业税改征增值税试点实施办法》附录第一条第（五）项
+原文: "金融商品转让，是指转让外汇、有价证券、非货物期货和其他金融商品所有权的业务活动。其他金融商品转让包括基金、信托、理财产品等各类资产管理产品和各种金融衍生品的转让。"
+适用性: 明确了上市公司股票（有价证券）的转让属于增值税应税范围，而未公开发行的非上市公司股权不在此列。
+官方来源: 《关于全面推开营业税改征增值税试点的通知》（财税〔2016〕36号） [18]
+发布机构: 财政部、国家税务总局
+条款: 附件2《营业税改征增值税试点有关事项的规定》第一条第（三）款
+原文: "金融商品转让，按照卖出价扣除买入价后的余额为销售额。转让金融商品出现的正负差，按盈亏相抵后的余额为销售额。"
+适用性: 确立了金融商品转让的差额计税原则。若被认定为应税交易，需计算卖出价与买入价的差额。
+2025年适用的资产重组豁免规则（历史规则）
+官方来源: 《国家税务总局关于纳税人资产重组有关增值税问题的公告》（2011年第13号） [19]
+发布机构: 国家税务总局
+条款: 正文
+原文: "纳税人在资产重组过程中，通过合并、分立、出售、置换等方式，将全部或者部分实物资产以及与其相关联的债权、负债和劳动力一并转让给其他单位和个人，不属于增值税的征税范围，其中涉及的货物转让，不征收增值税。"
+适用性: 这是2025年5月交易发生时有效的核心重组豁免文件。其局限性在于仅明确了“货物”（及后续36号文补充的不动产、土地使用权），未明文包含金融商品。
+2026年最新资产重组豁免规则（现行规则）
+官方来源: 《财政部 税务总局关于增值税进项税额抵扣等有关事项的公告》（2026年第13号） [2]
+发布机构: 财政部、国家税务总局
+条款: 第二条第（一）款
+原文: "（一）纳税人通过合并、分立、出售、置换等方式实施资产重组，同时符合下列条件的，不属于增值税应税交易和增值税法实施条例第二十二条规定的不得抵扣非应税交易，涉及的货物、金融商品、无形资产、不动产（以下统称资产）转让，不征收增值税，对应的进项税额可以按规定从销项税额中抵扣：1.资产重组的标的是可以相对独立运营的经营业务。2.纳税人实施资产重组时，应当将全部或者部分资产，与相关联的对应债权、负债和员工共同组成资产包，一并转让。资产包中应当同时包括资产、债权、负债和员工。3.资产重组应当具有合理的商业目的，且不以减少、免除、推迟缴纳增值税税款或者提前退税、多退税款为主要目的。4.资产重组的转让方属于一般..."
+适用性: 自2026年1月1日起施行。首次在国家层面明确将“金融商品”纳入重组不征收增值税的范围，彻底解决了历史争议。
+证券非交易过户程序规则
+官方来源: 《中国证券登记结算有限责任公司证券非交易过户业务实施细则（适用于继承、捐赠等情形）》 [17]
+发布机构: 中国证券登记结算有限责任公司 (CSDC)
+条款: 第三条
+原文: "本细则规定的证券非交易过户业务包括以下情形：……（四）法人终止所涉证券过户；"
+适用性: 构成本案吸收合并后，母公司向中登公司申请股票非交易过户的直接程序依据。
+D. 执法实践与专业机构观察分析
+由于我国实行成文法系，且关于吸收合并中股票过户的增值税争议缺乏最高人民法院的公开指导性案例，本节主要依据专业税务机构的观察及基层税务机关的执法实践进行分析。
+基层税务机关的从严执法倾向（2026年以前）
+根据普华永道（PwC）[8]及立信税务 [20] 等专业机构的实务观察，在《2026年第13号公告》[2] 出台之前，基层税务机关在处理企业注销、吸收合并导致的股票非交易过户时，普遍倾向于严格的字面解释。
+定性争议：税务机关通常认为，非交易过户仅是证券结算机构层面的操作概念。在税法实质上，只要股票所有权发生转移且存在对价（吸收合并中注销被合并方股权即为对价），即构成《财税〔2016〕36号》[18] 规定的“金融商品转让”。
+豁免条款的排斥适用：由于《国家税务总局公告2011年第13号》[19] 及《财税〔2016〕36号》附件2 [18] 采取的是正向列举方式（仅列举了货物、不动产、土地使用权），税务稽查部门往往拒绝将“股票”扩大解释为免税资产包的一部分 [20]。
+公允价值核定征收的实务风险
+在金杜律师事务所（KWM）关于“价格明显偏低且无正当理由”的实务分析中指出 [13]，对于关联企业间（如母子公司）的资产划转，企业常以“无对价”或“按账面净值结转”进行会计处理。然而，在增值税执法实践中，税务机关通常不认可“内部重组”或“账面净值”作为阻却价格核定的法定“正当理由” [13]。
+在多起历史税务稽查实务中，若企业未能成功主张重组豁免，税务机关会直接依据股票过户日（或合并基准日）的二级市场收盘价作为公允价值，核定其“卖出价”，并据此要求企业补缴6%的增值税及滞纳金 [8][20]。
+E. 详细法律分析
+问题一：标的股票性质与增值税的根本触发要件
+A. 适用法律框架
+根据《财税〔2016〕36号》附件1 [18]，增值税法下的“金融商品转让”严格限定为外汇、有价证券、非货物期货等。
+B. 事实分析与应用
+客户在查询中仅提及“子公司持有的股票”，未明确是上市公司股票还是非上市企业股权。
+若为非上市公司股权：非上市股权不属于“有价证券”。因此，其过户转移根本不属于增值税的征税范围。母公司可直接凭合并协议及市监局注销证明办理变更，无增值税风险。
+若为上市公司股票（含A股、新三板等）：属于标准的有价证券，其所有权由子公司转移至母公司，触发了增值税法上的“金融商品转让”初步定性 [18]。
+问题二：2025年5月吸收合并的重组豁免适用性争议
+A. 适用法律框架
+本案交易发生在2025年5月，受《国家税务总局公告2011年第13号》[19] 约束。该公告规定，将实物资产及关联债权、负债、劳动力一并转让的，不征收增值税。
+B. 事实分析与应用
+母子公司吸收合并天然满足“资产、负债、劳动力一并转移”的实质要件，因为子公司的主体资格消灭，其全部身家由母公司概括承受。然而，法律文本的滞后性导致了重大风险：2011年13号文 [19] 仅明确了“货物”不征税。子公司持有的股票作为金融资产，在2025年的时点上，处于法律条文的“盲区” [20]。
+C. 潜在抗辩
+企业可主张“实质重于形式”及“税收中性”原则。股票投资本质上属于企业的资产，剥离股票将破坏重组资产包的完整性。对其单独征收流转税，违背了鼓励企业重组的政策初衷 [8]。
+问题三：“无对价”与“账面净值”能否阻却公允价值核定？
+A. 适用法律框架
+《财税〔2016〕36号》[18] 规定金融商品转让按“卖出价扣除买入价”计税。若价格明显偏低且无正当理由，税务机关有权核定销售额。
+B. 事实分析与应用
+客户提出“吸收合并没有支付对价，会计上是按账面净值做的账”。
+在企业所得税领域（如财税〔2014〕109号文），100%控股母子公司间的划转确实可以按账面净值进行特殊性税务处理。但是，增值税法与企业所得税法是相互独立的 [13]。现行增值税法规中，没有任何条款规定“按企业会计准则以账面净值结转”可以作为增值税计税价格偏低的法定“正当理由” [13]。
+C. 法律后果
+如果税务机关拒绝给予重组豁免，他们将视该过户为“有偿转让”（以注销子公司股权为对价），并认定“无对价/账面净值”属于价格明显偏低。税务局将按过户日股票的公允价值（市值）核定卖出价，导致企业面临极高的增值税负 [20]。
+问题四：2026年新规的溯及力与救济应用
+A. 适用法律框架
+《2026年第13号公告》[2] 明确规定，自2026年1月1日起，符合条件的资产重组中涉及的“金融商品”转让，不征收增值税。
+B. 事实分析与应用
+虽然客户的合并发生在2025年5月，根据法不溯及既往原则，税务局可能拒绝直接适用2026年新规 [2]。但是，该新规的发布证实了国家税务总局认可“金融商品随资产包一并转让不应征收增值税”的法理逻辑 [8]。
+C. 法律后果与抗辩策略
+在实务应对中，企业应将《2026年第13号公告》[2] 作为核心说理工具。主张2026年新规并非“创设”了新的免税待遇，而是对2011年13号文 [19] 在营改增后遗留漏洞的“修补与明确”。通过证明本案吸收合并完全符合新规要求的“四大要件”（独立业务、四位一体打包、合理商业目的、纳税人身份对等），争取主管税务机关的认可，出具不征税证明或允许零申报。
+F. 缺失事实与信息缺口
+为提供最终的确切结论，需进一步澄清以下关键事实：
+标的股票的具体类型：是上市公司流通股、限售股，还是非上市公司的股权？（直接决定是否属于增值税征税范围）。
+税务清算状态：被吸收合并的子公司目前是否已完成税务注销（清税）程序？主管税务机关是否已对该笔股票过户提出明确的税务处理意见？
+股票的历史成本与当前市值：若最终必须按公允价值纳税，股票的原始买入价与过户日市值的差额是多少？（用于量化潜在的增值税敞口）。
+子公司的纳税人身份：子公司是一般纳税人还是小规模纳税人？（影响税率及2026年新规中“身份对等”条件的适用）。
+G. 实务影响与合规建议
+股票过户的程序性合规
+根据中国结算（CSDC）的《证券非交易过户业务实施细则》[17]，因法人终止（吸收合并）申请过户，CSDC柜台主要审查的是市监局出具的法人注销证明及合并协议，通常不强制要求单独提供增值税完税凭证（除非涉及个人所得税或特定限售股）。
+实务堵点：
+企业在取得市监局的注销证明前，必须先获得税务局的《清税证明》。如果在税务清算环节，主管税务局认定该股票过户需缴纳增值税且企业未缴纳，子公司将无法注销，进而导致CSDC的非交易过户程序彻底停滞。
+历史成本的继承问题（防范双重征税）
+如果企业成功争取到“不征收增值税”的待遇，母公司未来在二级市场减持该股票时，其增值税的“买入价”应如何确定？
+根据《2026年第13号公告》[2] 的精神，由于重组环节未征收增值税，母公司应当“穿透”合并行为，合法继承子公司最初取得该股票时的原始实际成本作为买入价。企业必须妥善保存子公司当年的原始购买凭证、交割单等，以备未来减持抵扣之需。
+H. 战略建议
+短期应对建议（税务清算与过户阶段）
+定性排查与隔离：立即核实股票性质。若包含非上市股权，应将其与上市公司股票在重组报告中分类列示，明确主张非上市股权不属增值税范围，缩小争议敞口。
+准备“实质性重组”证据包：严格对照《2026年第13号公告》[2] 的四大条件，准备合并协议、员工安置方案、债权债务承继清单。向主管税务局提交《关于吸收合并中金融商品转移适用资产重组不征税政策的请示》。
+运用2026新规进行政策博弈：在与税务局沟通时，重点强调2025年“无对价、按账面净值”的合并行为完全符合2026年新规 [2] 的实质要件。主张若强行按公允价值征税，将严重违背国家支持企业重组、保持税收中性的宏观政策导向。
+备选方案（若税务局强硬要求征税）
+做大买入价以压缩税基：若税务局坚持按《财税〔2016〕36号》[18] 征税，企业应穷尽规则做大“买入价”。例如，若为限售股，主张按实际成本价与法定买入价孰高原则确定扣除额，最大限度降低“卖出价（市值）- 买入价”的差额。
+要求确认新的计税基础：若本次过户被迫按公允价值缴纳了增值税，必须要求税务机关书面确认：母公司取得该股票的增值税新买入价已提升至本次核定的公允价值。以此确保未来减持时不再被重复征税。
+I. 结论
+综合上述分析，2025年5月发生的母子公司吸收合并涉及的股票非交易过户，在当时的增值税法规（财税〔2016〕36号）下处于政策模糊地带，面临被税务机关按公允价值核定征收“金融商品转让”增值税的高风险。“无对价”和“按账面净值结转”在增值税法上不能作为直接免税或平价结转的法定理由。
+然而，随着《2026年第13号公告》的施行，国家已明确将金融商品纳入资产重组不征税范围。企业应以此立法精神为核心抗辩武器，向主管税务机关证明该吸收合并系“资产、负债、员工”的整体打包转移，具有合理商业目的，全力争取“不征收增值税”的定性，从而在不产生额外税务成本的前提下，顺利完成税务注销与中登公司的非交易过户手续。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>错误，没有答出无偿转让股票的增值税关键法规。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通模式对，pro模式错，经提醒之后pro可以答对</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>核心发现
+重组一方中存在自然人股东，不影响企业重组中企业当事方适用特殊性税务处理。根据国家税务总局公告[2015]48号第一条，股权收购中转让方、合并中被合并企业股东和分立中被分立企业股东可以是自然人，但自然人应按个人所得税的相关规定进行税务处理。
+自然人股东不能适用企业所得税特殊性税务处理的递延纳税规则。特殊性税务处理是企业所得税法下的制度安排，个人所得税法下目前没有对应的企业重组递延纳税规定，自然人股东一般应在交易当期缴纳个人所得税。
+实务中存在个别地方税务机关认可自然人股东递延纳税的案例，但存在较高不确定性。
+风险评估
+高风险：若企业重组中存在自然人股东，且未经主管税务机关确认即对自然人适用递延纳税，存在被追缴税款及加收滞纳金的风险。
+中风险：部分地区税务机关对混合股东结构下企业方能否适用特殊性税务处理可能持从严态度，需提前沟通。
+低风险：企业当事方在满足59号文条件的前提下适用特殊性税务处理，法律依据较为充分，风险较低。
+核心建议
+在企业重组中，居民企业当事方和自然人股东应分别适用不同的税务处理规则——企业方适用企业所得税特殊性税务处理，自然人股东按个人所得税法当期纳税。
+重组前应与主管税务机关充分沟通，确认对自然人股东的处理口径。
+若需为自然人股东争取递延纳税效果，可考虑通过调整交易架构（如先由企业持股平台持有股权再进行重组）等方式实现。
+一、上位法依据
+（一）企业所得税法
+《中华人民共和国企业所得税法》第二十条规定："本章规定的收入、扣除的具体范围、标准和资产的税务处理的具体办法，由国务院财政、税务主管部门规定。"《中华人民共和国企业所得税法实施条例》第七十五条规定："除国务院财政、税务主管部门另有规定外，企业在重组过程中，应当在交易发生时确认有关资产的转让所得或者损失，相关资产应当按照交易价格重新确定计税基础。"这为企业重组特殊性税务处理（即递延确认所得）提供了上位法授权基础——国务院财政、税务主管部门可以另行规定例外情形。
+（二）个人所得税法
+《中华人民共和国个人所得税法》第二条将"财产转让所得"列为应税所得，第三条第（三）项规定财产转让所得适用20%比例税率，第六条第（五）项规定"财产转让所得，以转让财产的收入额减除财产原值和合理费用后的余额，为应纳税所得额"。个人所得税法及其实施条例中，目前没有类似于企业所得税法下企业重组特殊性税务处理（递延纳税）的规定。
+二、自然人股东是否影响企业重组适用特殊性税务处理？
+不影响。 国家税务总局公告[2015]48号第一条明确规定1：
+"按照重组类型，企业重组的当事各方是指：
+（一）债务重组中当事各方，指债务人、债权人。
+（二）股权收购中当事各方，指收购方、转让方及被收购企业。
+（三）资产收购中当事各方，指收购方、转让方。
+（四）合并中当事各方，指合并企业、被合并企业及被合并企业股东。
+（五）分立中当事各方，指分立企业、被分立企业及被分立企业股东。
+上述重组交易中，股权收购中转让方、合并中被合并企业股东和分立中被分立企业股东，可以是自然人。
+当事各方中的自然人应按个人所得税的相关规定进行税务处理。"
+该规定明确了两个要点：
+自然人可以作为重组当事方参与企业重组，其存在本身不影响重组交易的法律定性；
+自然人的税务处理独立于企业所得税的特殊性税务处理，应按个人所得税法另行处理。
+这意味着，在企业重组中，只要满足财税[2009]59号2第五条规定的五个条件（合理商业目的、股权/资产比例达标、经营连续性、股权支付比例达标、股东不转让所获股权），参与交易的居民企业当事方仍可适用特殊性税务处理，自然人股东的存在不会导致整个重组交易无法适用特殊性税务处理。
+三、自然人能否适用特殊性税务处理递延缴纳个人所得税？
+原则上不能。 理由如下：
+（一）特殊性税务处理是企业所得税制度
+财税[2009]59号2的标题即为"关于企业重组业务企业所得税处理若干问题的通知"，其法律依据是《企业所得税法》第二十条和《实施条例》第七十五条。特殊性税务处理的制度设计——暂不确认资产转让所得、以原计税基础确定新取得资产的计税基础——是企业所得税法下的特例规则，其适用主体为居民企业纳税人。
+（二）个人所得税法无对应递延纳税规定
+《个人所得税法》及其实施条例中，没有关于企业重组中自然人股东递延确认财产转让所得的规定。自然人因企业重组而转让股权，属于《个人所得税法》第二条规定的"财产转让所得"，应按照第六条第（五）项"以转让财产的收入额减除财产原值和合理费用后的余额"计算应纳税所得额，在交易当期缴纳个人所得税。
+（三）48号公告的明确指引
+国家税务总局公告[2015]48号第一条最后一款明确："当事各方中的自然人应按个人所得税的相关规定进行税务处理。"这一规定将自然人股东的税务处理与企业所得税特殊性税务处理明确分离，表明自然人股东不能因企业方适用特殊性税务处理而自动获得递延纳税待遇。
+（四）NTPS分析确认
+NTPS中国税务热点解析《子公司反向吸收合并母公司的企业所得税处理》3中明确指出：
+"59号文下的特殊性税务处理仅适用于居民企业纳税人。若母公司的原股东中存在自然人股东，根据国家税务总局公告[2015]48号文件，'股权收购中转让方、合并中被合并企业股东和分立中被分立企业股东，可以是自然人，自然人应按个人所得税的相关规定进行税务处理'。也就是说，在满足59号文STT其他条件的前提下，参与交易的居民企业股东和被合并企业仍可适用STT，但个人股东应按照个人所得税法处理（除有特别个人所得税文件规定，个人股东一般应在交易当期缴纳个人所得税）。"
+四、实务中的特殊情形与争议
+（一）个别案例中自然人股东获得递延纳税待遇
+在NTPS分析3中，提到了几个公开披露的案例：
+新亚强硅化学股份有限公司案例中，公司披露"本次吸收合并符合特殊性税务处理的条件……吉林新亚强的自然人股东不需要就本次吸收合并缴纳个人所得税"，理由是被合并方不需要进行清算、未发生利润分配行为、未进行转增股本处理。该案例取得了当地税务机关的盖章确认。
+华达汽车科技股份有限公司案例中，合并双方向税务局进行了特殊性税务处理备案。
+但NTPS分析同时提醒："考虑到这些案例披露的税务处理从理论层面与48号公告的规定存在偏差，我们理解可能存在一定税收争议和风险。"
+（二）合伙企业股东的问题
+NTPS分析3还指出："对于股权转让方、被合并企业股东和被分立企业股东是合伙企业的情况，实务上北京和较多基层税务局都不支持合伙企业股东适用STT，也即应由合伙企业的各合伙人在交易当期确认所得，缴纳所得税。"
+（三）建议
+鉴于上述不确定性，在企业重组涉及自然人股东时，建议：
+提前与主管税务机关沟通，确认对自然人股东的处理口径；
+考虑调整交易架构，如通过企业持股平台间接持股，使自然人股东不直接作为重组当事方；
+关注个人所得税领域是否有新的政策出台，目前个人所得税法下尚无企业重组递延纳税的一般性规定。
+五、策略路径比较
+策略路径	可行性	法律法规依据	关键法律与实务风险
+路径一：企业方适用特殊性税务处理，自然人当期缴纳个税	高	48号公告第一条明确分离处理；59号文适用于居民企业	自然人股东需在交易当期缴纳个税，可能面临现金流压力
+路径二：争取自然人也递延纳税	低（仅个别地方可能认可）	无明确的个人所得税法依据；个别案例依赖地方税局个案确认	与48号公告原则存在偏差，存在被追缴税款及滞纳金的风险；不同地区口径不一
+路径三：调整架构，由企业持股平台代持后再重组	中	通过架构调整使自然人成为间接股东，避免直接作为重组当事方	需提前规划，可能涉及额外交易步骤和成本；需注意架构调整本身的税务影响及商业合理性
+引用文件
+[1] 国家税务总局关于企业重组业务企业所得税征收管理若干问题的公告
+[2] 财政部、国家税务总局关于企业重组业务企业所得税处理若干问题的通知
+[3] 子公司反向吸收合并母公司的企业所得税处理
+[4] 财政部、国家税务总局关于促进企业重组有关企业所得税处理问题的通知
+[5] 国家税务总局关于发布《企业重组业务企业所得税管理办法》的公告
+[6] 国家税务总局关于非居民企业股权转让适用特殊性税务处理有关问题的公告
+[7] 国家税务总局关于资产（股权）划转企业所得税征管问题的公告
+[8] 所得税疑难案例解析问答概要(2024年1月)
+[9] 中国税务热点解析：企业所得税疑难问题探讨
+上位法文件（无需生成访问链接）：
+《中华人民共和国企业所得税法》
+《中华人民共和国企业所得税法实施条例》
+《中华人民共和国个人所得税法》
+《中华人民共和国个人所得税法实施条例》</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>回答正确</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>NA</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -824,7 +3476,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -903,6 +3555,60 @@
       <name val="Segoe UI Emoji"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="1"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Cambria Math"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -985,7 +3691,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1028,6 +3734,27 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1342,8 +4069,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A95C7D08-3D82-4A99-A37D-BA4B4F68B637}">
+  <dimension ref="A1:T7"/>
   <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.25" style="4" customWidth="1"/>
@@ -1364,7 +4091,7 @@
     <col min="21" max="16384" width="9.125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1419,11 +4146,8 @@
       <c r="R1" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="S1" s="4" t="s">
-        <v>34</v>
-      </c>
     </row>
-    <row r="2" spans="1:19" ht="406.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" ht="409.5" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1478,14 +4202,240 @@
       <c r="R2" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="S2" s="4" t="s">
+    </row>
+    <row r="3" spans="1:20" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="19">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="D3" s="20">
+        <v>96</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="409.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="M4" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="P4" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q4" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="R4" s="12"/>
+    </row>
+    <row r="5" spans="1:20" ht="409.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>6</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M5" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="O5" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="P5" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q5" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="R5" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="S5" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="T5" s="4" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="409.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G6" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="H6" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="M6" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="N6" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="O6" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="P6" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="Q6" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="R6" s="12"/>
+      <c r="S6" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="T6" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="409.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="8">
+        <v>12</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="F7" s="8"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="O7" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="P7" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q7" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="R7" s="12" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>